--- a/research/traditional_assets/database/data/qatar/qatar_utility_general.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_utility_general.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06796149377713223</v>
+        <v>0.06793403228335509</v>
       </c>
       <c r="C2">
-        <v>6732.314573581886</v>
+        <v>6669.340423998906</v>
       </c>
       <c r="D2">
-        <v>5870.514573581886</v>
+        <v>5873.845423998906</v>
       </c>
       <c r="E2">
-        <v>-1886.6</v>
+        <v>-1820.295</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>66.30500000000001</v>
       </c>
       <c r="G2">
         <v>861.8</v>
@@ -1457,28 +1457,28 @@
         <v>405.805</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.3351415</v>
       </c>
       <c r="N2">
-        <v>405.805</v>
+        <v>402.4698585</v>
       </c>
       <c r="O2">
-        <v>40.5805</v>
+        <v>40.24698585</v>
       </c>
       <c r="P2">
-        <v>365.2245</v>
+        <v>362.22287265</v>
       </c>
       <c r="Q2">
-        <v>370.7945</v>
+        <v>367.79287265</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06796149377713223</v>
+        <v>0.06816296190237889</v>
       </c>
       <c r="T2">
-        <v>0.4441974458563937</v>
+        <v>0.4482356044550881</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>121.6754971265837</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06793403228335509</v>
+        <v>0.06790657078957797</v>
       </c>
       <c r="C3">
-        <v>6669.340423998906</v>
+        <v>6606.370056320505</v>
       </c>
       <c r="D3">
-        <v>5873.845423998906</v>
+        <v>5877.180056320504</v>
       </c>
       <c r="E3">
-        <v>-1820.295</v>
+        <v>-1753.99</v>
       </c>
       <c r="F3">
-        <v>66.30500000000001</v>
+        <v>132.61</v>
       </c>
       <c r="G3">
         <v>861.8</v>
@@ -1539,28 +1539,28 @@
         <v>405.805</v>
       </c>
       <c r="M3">
-        <v>3.3351415</v>
+        <v>6.670283</v>
       </c>
       <c r="N3">
-        <v>402.4698585</v>
+        <v>399.134717</v>
       </c>
       <c r="O3">
-        <v>40.24698585</v>
+        <v>39.9134717</v>
       </c>
       <c r="P3">
-        <v>362.22287265</v>
+        <v>359.2212453</v>
       </c>
       <c r="Q3">
-        <v>367.79287265</v>
+        <v>364.7912453</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06816296190237889</v>
+        <v>0.06836854162201834</v>
       </c>
       <c r="T3">
-        <v>0.4482356044550881</v>
+        <v>0.452356174453756</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>121.6754971265837</v>
+        <v>60.83774856329184</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06790657078957797</v>
+        <v>0.06787910929580084</v>
       </c>
       <c r="C4">
-        <v>6606.370056320505</v>
+        <v>6543.403476991404</v>
       </c>
       <c r="D4">
-        <v>5877.180056320504</v>
+        <v>5880.518476991404</v>
       </c>
       <c r="E4">
-        <v>-1753.99</v>
+        <v>-1687.685</v>
       </c>
       <c r="F4">
-        <v>132.61</v>
+        <v>198.915</v>
       </c>
       <c r="G4">
         <v>861.8</v>
@@ -1621,28 +1621,28 @@
         <v>405.805</v>
       </c>
       <c r="M4">
-        <v>6.670283</v>
+        <v>10.0054245</v>
       </c>
       <c r="N4">
-        <v>399.134717</v>
+        <v>395.7995755</v>
       </c>
       <c r="O4">
-        <v>39.9134717</v>
+        <v>39.57995755</v>
       </c>
       <c r="P4">
-        <v>359.2212453</v>
+        <v>356.21961795</v>
       </c>
       <c r="Q4">
-        <v>364.7912453</v>
+        <v>361.78961795</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06836854162201834</v>
+        <v>0.06857836009876375</v>
       </c>
       <c r="T4">
-        <v>0.452356174453756</v>
+        <v>0.4565617046585819</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.83774856329184</v>
+        <v>40.55849904219457</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06787910929580084</v>
+        <v>0.0678516478020237</v>
       </c>
       <c r="C5">
-        <v>6543.403476991404</v>
+        <v>6480.44069247097</v>
       </c>
       <c r="D5">
-        <v>5880.518476991404</v>
+        <v>5883.86069247097</v>
       </c>
       <c r="E5">
-        <v>-1687.685</v>
+        <v>-1621.38</v>
       </c>
       <c r="F5">
-        <v>198.915</v>
+        <v>265.22</v>
       </c>
       <c r="G5">
         <v>861.8</v>
@@ -1703,28 +1703,28 @@
         <v>405.805</v>
       </c>
       <c r="M5">
-        <v>10.0054245</v>
+        <v>13.340566</v>
       </c>
       <c r="N5">
-        <v>395.7995755</v>
+        <v>392.464434</v>
       </c>
       <c r="O5">
-        <v>39.57995755</v>
+        <v>39.2464434</v>
       </c>
       <c r="P5">
-        <v>356.21961795</v>
+        <v>353.2179906</v>
       </c>
       <c r="Q5">
-        <v>361.78961795</v>
+        <v>358.7879906</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06857836009876375</v>
+        <v>0.06879254979377469</v>
       </c>
       <c r="T5">
-        <v>0.4565617046585819</v>
+        <v>0.4608548500760085</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.55849904219457</v>
+        <v>30.41887428164592</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0678516478020237</v>
+        <v>0.06782418630824658</v>
       </c>
       <c r="C6">
-        <v>6480.44069247097</v>
+        <v>6417.481709233265</v>
       </c>
       <c r="D6">
-        <v>5883.86069247097</v>
+        <v>5887.206709233265</v>
       </c>
       <c r="E6">
-        <v>-1621.38</v>
+        <v>-1555.075</v>
       </c>
       <c r="F6">
-        <v>265.22</v>
+        <v>331.525</v>
       </c>
       <c r="G6">
         <v>861.8</v>
@@ -1785,28 +1785,28 @@
         <v>405.805</v>
       </c>
       <c r="M6">
-        <v>13.340566</v>
+        <v>16.6757075</v>
       </c>
       <c r="N6">
-        <v>392.464434</v>
+        <v>389.1292925</v>
       </c>
       <c r="O6">
-        <v>39.2464434</v>
+        <v>38.91292925</v>
       </c>
       <c r="P6">
-        <v>353.2179906</v>
+        <v>350.21636325</v>
       </c>
       <c r="Q6">
-        <v>358.7879906</v>
+        <v>355.78636325</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06879254979377469</v>
+        <v>0.06901124874552271</v>
       </c>
       <c r="T6">
-        <v>0.4608548500760085</v>
+        <v>0.4652383775022229</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.41887428164592</v>
+        <v>24.33509942531673</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06782418630824658</v>
+        <v>0.06779672481446944</v>
       </c>
       <c r="C7">
-        <v>6417.481709233265</v>
+        <v>6354.526533767089</v>
       </c>
       <c r="D7">
-        <v>5887.206709233265</v>
+        <v>5890.556533767089</v>
       </c>
       <c r="E7">
-        <v>-1555.075</v>
+        <v>-1488.77</v>
       </c>
       <c r="F7">
-        <v>331.525</v>
+        <v>397.83</v>
       </c>
       <c r="G7">
         <v>861.8</v>
@@ -1867,28 +1867,28 @@
         <v>405.805</v>
       </c>
       <c r="M7">
-        <v>16.6757075</v>
+        <v>20.010849</v>
       </c>
       <c r="N7">
-        <v>389.1292925</v>
+        <v>385.794151</v>
       </c>
       <c r="O7">
-        <v>38.91292925</v>
+        <v>38.57941510000001</v>
       </c>
       <c r="P7">
-        <v>350.21636325</v>
+        <v>347.2147359</v>
       </c>
       <c r="Q7">
-        <v>355.78636325</v>
+        <v>352.7847359</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06901124874552271</v>
+        <v>0.06923460086645686</v>
       </c>
       <c r="T7">
-        <v>0.4652383775022229</v>
+        <v>0.4697151714694206</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.33509942531673</v>
+        <v>20.27924952109728</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06779672481446944</v>
+        <v>0.06776926332069232</v>
       </c>
       <c r="C8">
-        <v>6354.526533767089</v>
+        <v>6291.575172576012</v>
       </c>
       <c r="D8">
-        <v>5890.556533767089</v>
+        <v>5893.910172576012</v>
       </c>
       <c r="E8">
-        <v>-1488.77</v>
+        <v>-1422.465</v>
       </c>
       <c r="F8">
-        <v>397.83</v>
+        <v>464.1349999999999</v>
       </c>
       <c r="G8">
         <v>861.8</v>
@@ -1949,28 +1949,28 @@
         <v>405.805</v>
       </c>
       <c r="M8">
-        <v>20.010849</v>
+        <v>23.3459905</v>
       </c>
       <c r="N8">
-        <v>385.794151</v>
+        <v>382.4590095</v>
       </c>
       <c r="O8">
-        <v>38.57941510000001</v>
+        <v>38.24590095000001</v>
       </c>
       <c r="P8">
-        <v>347.2147359</v>
+        <v>344.21310855</v>
       </c>
       <c r="Q8">
-        <v>352.7847359</v>
+        <v>349.78310855</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06923460086645686</v>
+        <v>0.06946275625880893</v>
       </c>
       <c r="T8">
-        <v>0.4697151714694206</v>
+        <v>0.4742882405756977</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.27924952109728</v>
+        <v>17.38221387522625</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0677692633206923</v>
+        <v>0.06774180182691518</v>
       </c>
       <c r="C9">
-        <v>6291.575172576014</v>
+        <v>6228.627632178432</v>
       </c>
       <c r="D9">
-        <v>5893.910172576014</v>
+        <v>5897.267632178432</v>
       </c>
       <c r="E9">
-        <v>-1422.465</v>
+        <v>-1356.16</v>
       </c>
       <c r="F9">
-        <v>464.135</v>
+        <v>530.4400000000001</v>
       </c>
       <c r="G9">
         <v>861.8</v>
@@ -2031,28 +2031,28 @@
         <v>405.805</v>
       </c>
       <c r="M9">
-        <v>23.3459905</v>
+        <v>26.681132</v>
       </c>
       <c r="N9">
-        <v>382.4590095</v>
+        <v>379.123868</v>
       </c>
       <c r="O9">
-        <v>38.24590095</v>
+        <v>37.9123868</v>
       </c>
       <c r="P9">
-        <v>344.21310855</v>
+        <v>341.2114812</v>
       </c>
       <c r="Q9">
-        <v>349.78310855</v>
+        <v>346.7814812</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06946275625880893</v>
+        <v>0.06969587155099476</v>
       </c>
       <c r="T9">
-        <v>0.4742882405756979</v>
+        <v>0.4789607242277636</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.38221387522624</v>
+        <v>15.20943714082296</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06774180182691518</v>
+        <v>0.06771434033313806</v>
       </c>
       <c r="C10">
-        <v>6228.627632178432</v>
+        <v>6165.683919107599</v>
       </c>
       <c r="D10">
-        <v>5897.267632178432</v>
+        <v>5900.628919107598</v>
       </c>
       <c r="E10">
-        <v>-1356.16</v>
+        <v>-1289.855</v>
       </c>
       <c r="F10">
-        <v>530.4400000000001</v>
+        <v>596.745</v>
       </c>
       <c r="G10">
         <v>861.8</v>
@@ -2113,28 +2113,28 @@
         <v>405.805</v>
       </c>
       <c r="M10">
-        <v>26.681132</v>
+        <v>30.0162735</v>
       </c>
       <c r="N10">
-        <v>379.123868</v>
+        <v>375.7887265</v>
       </c>
       <c r="O10">
-        <v>37.9123868</v>
+        <v>37.57887265</v>
       </c>
       <c r="P10">
-        <v>341.2114812</v>
+        <v>338.20985385</v>
       </c>
       <c r="Q10">
-        <v>346.7814812</v>
+        <v>343.77985385</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06969587155099476</v>
+        <v>0.06993411025619566</v>
       </c>
       <c r="T10">
-        <v>0.4789607242277636</v>
+        <v>0.4837358998282265</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.20943714082296</v>
+        <v>13.51949968073152</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06771434033313806</v>
+        <v>0.06782187883936092</v>
       </c>
       <c r="C11">
-        <v>6165.683919107599</v>
+        <v>6086.238033674196</v>
       </c>
       <c r="D11">
-        <v>5900.628919107598</v>
+        <v>5887.488033674196</v>
       </c>
       <c r="E11">
-        <v>-1289.855</v>
+        <v>-1223.55</v>
       </c>
       <c r="F11">
-        <v>596.745</v>
+        <v>663.05</v>
       </c>
       <c r="G11">
         <v>861.8</v>
@@ -2195,45 +2195,45 @@
         <v>405.805</v>
       </c>
       <c r="M11">
-        <v>30.0162735</v>
+        <v>34.34598999999999</v>
       </c>
       <c r="N11">
-        <v>375.7887265</v>
+        <v>371.45901</v>
       </c>
       <c r="O11">
-        <v>37.57887265</v>
+        <v>37.145901</v>
       </c>
       <c r="P11">
-        <v>338.20985385</v>
+        <v>334.3131090000001</v>
       </c>
       <c r="Q11">
-        <v>343.77985385</v>
+        <v>339.883109</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06993411025619566</v>
+        <v>0.07017764315484547</v>
       </c>
       <c r="T11">
-        <v>0.4837358998282265</v>
+        <v>0.4886171904420331</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.1</v>
       </c>
       <c r="W11">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.51949968073152</v>
+        <v>11.81520753951189</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06782187883936092</v>
+        <v>0.06780791734558378</v>
       </c>
       <c r="C12">
-        <v>6086.238033674196</v>
+        <v>6021.635779548002</v>
       </c>
       <c r="D12">
-        <v>5887.488033674196</v>
+        <v>5889.190779548001</v>
       </c>
       <c r="E12">
-        <v>-1223.55</v>
+        <v>-1157.245</v>
       </c>
       <c r="F12">
-        <v>663.0500000000001</v>
+        <v>729.355</v>
       </c>
       <c r="G12">
         <v>861.8</v>
@@ -2277,28 +2277,28 @@
         <v>405.805</v>
       </c>
       <c r="M12">
-        <v>34.34599</v>
+        <v>37.780589</v>
       </c>
       <c r="N12">
-        <v>371.45901</v>
+        <v>368.024411</v>
       </c>
       <c r="O12">
-        <v>37.145901</v>
+        <v>36.8024411</v>
       </c>
       <c r="P12">
-        <v>334.3131090000001</v>
+        <v>331.2219699</v>
       </c>
       <c r="Q12">
-        <v>339.883109</v>
+        <v>336.7919699</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07017764315484547</v>
+        <v>0.07042664870290312</v>
       </c>
       <c r="T12">
-        <v>0.4886171904420331</v>
+        <v>0.4936081729797453</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.81520753951189</v>
+        <v>10.74109776319263</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06780791734558378</v>
+        <v>0.06779395585180666</v>
       </c>
       <c r="C13">
-        <v>6021.635779548002</v>
+        <v>5957.034510623733</v>
       </c>
       <c r="D13">
-        <v>5889.190779548001</v>
+        <v>5890.894510623732</v>
       </c>
       <c r="E13">
-        <v>-1157.245</v>
+        <v>-1090.94</v>
       </c>
       <c r="F13">
-        <v>729.355</v>
+        <v>795.66</v>
       </c>
       <c r="G13">
         <v>861.8</v>
@@ -2359,28 +2359,28 @@
         <v>405.805</v>
       </c>
       <c r="M13">
-        <v>37.780589</v>
+        <v>41.215188</v>
       </c>
       <c r="N13">
-        <v>368.024411</v>
+        <v>364.589812</v>
       </c>
       <c r="O13">
-        <v>36.8024411</v>
+        <v>36.4589812</v>
       </c>
       <c r="P13">
-        <v>331.2219699</v>
+        <v>328.1308308</v>
       </c>
       <c r="Q13">
-        <v>336.7919699</v>
+        <v>333.7008308</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07042664870290312</v>
+        <v>0.07068131346796211</v>
       </c>
       <c r="T13">
-        <v>0.4936081729797453</v>
+        <v>0.4987125869387693</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.74109776319263</v>
+        <v>9.846006282926576</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06779395585180666</v>
+        <v>0.06797889435802951</v>
       </c>
       <c r="C14">
-        <v>5957.034510623733</v>
+        <v>5868.240982539802</v>
       </c>
       <c r="D14">
-        <v>5890.894510623732</v>
+        <v>5868.405982539802</v>
       </c>
       <c r="E14">
-        <v>-1090.94</v>
+        <v>-1024.635</v>
       </c>
       <c r="F14">
-        <v>795.66</v>
+        <v>861.965</v>
       </c>
       <c r="G14">
         <v>861.8</v>
@@ -2441,45 +2441,45 @@
         <v>405.805</v>
       </c>
       <c r="M14">
-        <v>41.215188</v>
+        <v>46.1151275</v>
       </c>
       <c r="N14">
-        <v>364.589812</v>
+        <v>359.6898725</v>
       </c>
       <c r="O14">
-        <v>36.4589812</v>
+        <v>35.96898725</v>
       </c>
       <c r="P14">
-        <v>328.1308308</v>
+        <v>323.72088525</v>
       </c>
       <c r="Q14">
-        <v>333.7008308</v>
+        <v>329.29088525</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07068131346796211</v>
+        <v>0.07094183259543622</v>
       </c>
       <c r="T14">
-        <v>0.4987125869387693</v>
+        <v>0.503934343747426</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.846006282926576</v>
+        <v>8.799823875581826</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06797889435802951</v>
+        <v>0.06798023286425238</v>
       </c>
       <c r="C15">
-        <v>5868.240982539802</v>
+        <v>5801.773845967912</v>
       </c>
       <c r="D15">
-        <v>5868.405982539802</v>
+        <v>5868.243845967912</v>
       </c>
       <c r="E15">
-        <v>-1024.635</v>
+        <v>-958.3299999999998</v>
       </c>
       <c r="F15">
-        <v>861.965</v>
+        <v>928.2700000000001</v>
       </c>
       <c r="G15">
         <v>861.8</v>
@@ -2523,28 +2523,28 @@
         <v>405.805</v>
       </c>
       <c r="M15">
-        <v>46.1151275</v>
+        <v>49.66244500000001</v>
       </c>
       <c r="N15">
-        <v>359.6898725</v>
+        <v>356.142555</v>
       </c>
       <c r="O15">
-        <v>35.96898725</v>
+        <v>35.61425550000001</v>
       </c>
       <c r="P15">
-        <v>323.72088525</v>
+        <v>320.5282995</v>
       </c>
       <c r="Q15">
-        <v>329.29088525</v>
+        <v>326.0982995</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07094183259543622</v>
+        <v>0.07120841030727021</v>
       </c>
       <c r="T15">
-        <v>0.503934343747426</v>
+        <v>0.5092775367609351</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.799823875581826</v>
+        <v>8.17126502732598</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06798023286425238</v>
+        <v>0.06798157137047525</v>
       </c>
       <c r="C16">
-        <v>5801.773845967912</v>
+        <v>5735.306718355029</v>
       </c>
       <c r="D16">
-        <v>5868.243845967912</v>
+        <v>5868.081718355029</v>
       </c>
       <c r="E16">
-        <v>-958.3299999999998</v>
+        <v>-892.0249999999997</v>
       </c>
       <c r="F16">
-        <v>928.2700000000001</v>
+        <v>994.5750000000002</v>
       </c>
       <c r="G16">
         <v>861.8</v>
@@ -2605,28 +2605,28 @@
         <v>405.805</v>
       </c>
       <c r="M16">
-        <v>49.66244500000001</v>
+        <v>53.20976250000001</v>
       </c>
       <c r="N16">
-        <v>356.142555</v>
+        <v>352.5952375</v>
       </c>
       <c r="O16">
-        <v>35.61425550000001</v>
+        <v>35.25952375</v>
       </c>
       <c r="P16">
-        <v>320.5282995</v>
+        <v>317.33571375</v>
       </c>
       <c r="Q16">
-        <v>326.0982995</v>
+        <v>322.90571375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07120841030727021</v>
+        <v>0.07148126043585323</v>
       </c>
       <c r="T16">
-        <v>0.5092775367609351</v>
+        <v>0.5147464519629974</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.17126502732598</v>
+        <v>7.626514025504247</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06798157137047525</v>
+        <v>0.06809810987669812</v>
       </c>
       <c r="C17">
-        <v>5735.306718355029</v>
+        <v>5654.920163251351</v>
       </c>
       <c r="D17">
-        <v>5868.081718355029</v>
+        <v>5854.000163251351</v>
       </c>
       <c r="E17">
-        <v>-892.025</v>
+        <v>-825.7199999999998</v>
       </c>
       <c r="F17">
-        <v>994.5749999999999</v>
+        <v>1060.88</v>
       </c>
       <c r="G17">
         <v>861.8</v>
@@ -2687,45 +2687,45 @@
         <v>405.805</v>
       </c>
       <c r="M17">
-        <v>53.2097625</v>
+        <v>57.60578400000001</v>
       </c>
       <c r="N17">
-        <v>352.5952375</v>
+        <v>348.199216</v>
       </c>
       <c r="O17">
-        <v>35.25952375</v>
+        <v>34.8199216</v>
       </c>
       <c r="P17">
-        <v>317.33571375</v>
+        <v>313.3792944</v>
       </c>
       <c r="Q17">
-        <v>322.90571375</v>
+        <v>318.9492944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07148126043585323</v>
+        <v>0.07176060699606919</v>
       </c>
       <c r="T17">
-        <v>0.5147464519629974</v>
+        <v>0.5203455794317755</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.1</v>
       </c>
       <c r="W17">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.626514025504249</v>
+        <v>7.044518307397742</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06809810987669812</v>
+        <v>0.06810664838292099</v>
       </c>
       <c r="C18">
-        <v>5654.920163251351</v>
+        <v>5587.586097090086</v>
       </c>
       <c r="D18">
-        <v>5854.000163251351</v>
+        <v>5852.971097090086</v>
       </c>
       <c r="E18">
-        <v>-825.7199999999998</v>
+        <v>-759.4149999999997</v>
       </c>
       <c r="F18">
-        <v>1060.88</v>
+        <v>1127.185</v>
       </c>
       <c r="G18">
         <v>861.8</v>
@@ -2769,28 +2769,28 @@
         <v>405.805</v>
       </c>
       <c r="M18">
-        <v>57.60578400000001</v>
+        <v>61.20614550000001</v>
       </c>
       <c r="N18">
-        <v>348.199216</v>
+        <v>344.5988545</v>
       </c>
       <c r="O18">
-        <v>34.8199216</v>
+        <v>34.45988545</v>
       </c>
       <c r="P18">
-        <v>313.3792944</v>
+        <v>310.13896905</v>
       </c>
       <c r="Q18">
-        <v>318.9492944</v>
+        <v>315.70896905</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07176060699606919</v>
+        <v>0.07204668479869999</v>
       </c>
       <c r="T18">
-        <v>0.5203455794317755</v>
+        <v>0.526079625634741</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.044518307397742</v>
+        <v>6.630134877550816</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06810664838292099</v>
+        <v>0.06811518688914386</v>
       </c>
       <c r="C19">
-        <v>5587.586097090086</v>
+        <v>5520.252392661316</v>
       </c>
       <c r="D19">
-        <v>5852.971097090086</v>
+        <v>5851.942392661316</v>
       </c>
       <c r="E19">
-        <v>-759.4149999999997</v>
+        <v>-693.1099999999997</v>
       </c>
       <c r="F19">
-        <v>1127.185</v>
+        <v>1193.49</v>
       </c>
       <c r="G19">
         <v>861.8</v>
@@ -2851,28 +2851,28 @@
         <v>405.805</v>
       </c>
       <c r="M19">
-        <v>61.20614550000001</v>
+        <v>64.80650700000001</v>
       </c>
       <c r="N19">
-        <v>344.5988545</v>
+        <v>340.998493</v>
       </c>
       <c r="O19">
-        <v>34.45988545</v>
+        <v>34.0998493</v>
       </c>
       <c r="P19">
-        <v>310.13896905</v>
+        <v>306.8986437</v>
       </c>
       <c r="Q19">
-        <v>315.70896905</v>
+        <v>312.4686437</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07204668479869999</v>
+        <v>0.07233974010871203</v>
       </c>
       <c r="T19">
-        <v>0.526079625634741</v>
+        <v>0.5319535266231447</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.630134877550816</v>
+        <v>6.261794051020216</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06811518688914386</v>
+        <v>0.06829472539536673</v>
       </c>
       <c r="C20">
-        <v>5520.252392661317</v>
+        <v>5432.40033658743</v>
       </c>
       <c r="D20">
-        <v>5851.942392661316</v>
+        <v>5830.395336587429</v>
       </c>
       <c r="E20">
-        <v>-693.1099999999999</v>
+        <v>-626.8049999999998</v>
       </c>
       <c r="F20">
-        <v>1193.49</v>
+        <v>1259.795</v>
       </c>
       <c r="G20">
         <v>861.8</v>
@@ -2933,45 +2933,45 @@
         <v>405.805</v>
       </c>
       <c r="M20">
-        <v>64.806507</v>
+        <v>69.66666350000001</v>
       </c>
       <c r="N20">
-        <v>340.998493</v>
+        <v>336.1383365</v>
       </c>
       <c r="O20">
-        <v>34.0998493</v>
+        <v>33.61383365</v>
       </c>
       <c r="P20">
-        <v>306.8986437</v>
+        <v>302.52450285</v>
       </c>
       <c r="Q20">
-        <v>312.4686437</v>
+        <v>308.09450285</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07233974010871203</v>
+        <v>0.0726400313523046</v>
       </c>
       <c r="T20">
-        <v>0.5319535266231447</v>
+        <v>0.5379724622038545</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.1</v>
       </c>
       <c r="W20">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.261794051020217</v>
+        <v>5.824952417880611</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06829472539536673</v>
+        <v>0.06831226390158959</v>
       </c>
       <c r="C21">
-        <v>5432.40033658743</v>
+        <v>5363.998982133068</v>
       </c>
       <c r="D21">
-        <v>5830.395336587429</v>
+        <v>5828.298982133068</v>
       </c>
       <c r="E21">
-        <v>-626.8049999999998</v>
+        <v>-560.4999999999998</v>
       </c>
       <c r="F21">
-        <v>1259.795</v>
+        <v>1326.1</v>
       </c>
       <c r="G21">
         <v>861.8</v>
@@ -3015,28 +3015,28 @@
         <v>405.805</v>
       </c>
       <c r="M21">
-        <v>69.66666350000001</v>
+        <v>73.33333</v>
       </c>
       <c r="N21">
-        <v>336.1383365</v>
+        <v>332.47167</v>
       </c>
       <c r="O21">
-        <v>33.61383365</v>
+        <v>33.247167</v>
       </c>
       <c r="P21">
-        <v>302.52450285</v>
+        <v>299.224503</v>
       </c>
       <c r="Q21">
-        <v>308.09450285</v>
+        <v>304.794503</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0726400313523046</v>
+        <v>0.07294782987698699</v>
       </c>
       <c r="T21">
-        <v>0.5379724622038545</v>
+        <v>0.5441418711740823</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.824952417880611</v>
+        <v>5.533704796986582</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06831226390158959</v>
+        <v>0.06832980240781246</v>
       </c>
       <c r="C22">
-        <v>5363.998982133068</v>
+        <v>5295.599134651105</v>
       </c>
       <c r="D22">
-        <v>5828.298982133068</v>
+        <v>5826.204134651105</v>
       </c>
       <c r="E22">
-        <v>-560.4999999999998</v>
+        <v>-494.1949999999997</v>
       </c>
       <c r="F22">
-        <v>1326.1</v>
+        <v>1392.405</v>
       </c>
       <c r="G22">
         <v>861.8</v>
@@ -3097,28 +3097,28 @@
         <v>405.805</v>
       </c>
       <c r="M22">
-        <v>73.33333</v>
+        <v>76.99999650000001</v>
       </c>
       <c r="N22">
-        <v>332.47167</v>
+        <v>328.8050035</v>
       </c>
       <c r="O22">
-        <v>33.247167</v>
+        <v>32.88050035</v>
       </c>
       <c r="P22">
-        <v>299.224503</v>
+        <v>295.92450315</v>
       </c>
       <c r="Q22">
-        <v>304.794503</v>
+        <v>301.49450315</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07294782987698699</v>
+        <v>0.07326342076938286</v>
       </c>
       <c r="T22">
-        <v>0.5441418711740823</v>
+        <v>0.5504674677131765</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.533704796986582</v>
+        <v>5.270195044749125</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06832980240781246</v>
+        <v>0.06834734091403533</v>
       </c>
       <c r="C23">
-        <v>5295.599134651105</v>
+        <v>5227.200792517187</v>
       </c>
       <c r="D23">
-        <v>5826.204134651105</v>
+        <v>5824.110792517186</v>
       </c>
       <c r="E23">
-        <v>-494.1949999999999</v>
+        <v>-427.8899999999999</v>
       </c>
       <c r="F23">
-        <v>1392.405</v>
+        <v>1458.71</v>
       </c>
       <c r="G23">
         <v>861.8</v>
@@ -3179,28 +3179,28 @@
         <v>405.805</v>
       </c>
       <c r="M23">
-        <v>76.99999649999999</v>
+        <v>80.666663</v>
       </c>
       <c r="N23">
-        <v>328.8050035</v>
+        <v>325.138337</v>
       </c>
       <c r="O23">
-        <v>32.88050035</v>
+        <v>32.5138337</v>
       </c>
       <c r="P23">
-        <v>295.92450315</v>
+        <v>292.6245033</v>
       </c>
       <c r="Q23">
-        <v>301.49450315</v>
+        <v>298.1945033</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07326342076938286</v>
+        <v>0.07358710373594272</v>
       </c>
       <c r="T23">
-        <v>0.5504674677131765</v>
+        <v>0.5569552590353244</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.270195044749125</v>
+        <v>5.030640724533256</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06834734091403533</v>
+        <v>0.06836487942025819</v>
       </c>
       <c r="C24">
-        <v>5227.200792517187</v>
+        <v>5158.80395410929</v>
       </c>
       <c r="D24">
-        <v>5824.110792517186</v>
+        <v>5822.01895410929</v>
       </c>
       <c r="E24">
-        <v>-427.8899999999999</v>
+        <v>-361.5849999999998</v>
       </c>
       <c r="F24">
-        <v>1458.71</v>
+        <v>1525.015</v>
       </c>
       <c r="G24">
         <v>861.8</v>
@@ -3261,28 +3261,28 @@
         <v>405.805</v>
       </c>
       <c r="M24">
-        <v>80.666663</v>
+        <v>84.3333295</v>
       </c>
       <c r="N24">
-        <v>325.138337</v>
+        <v>321.4716705</v>
       </c>
       <c r="O24">
-        <v>32.5138337</v>
+        <v>32.14716705</v>
       </c>
       <c r="P24">
-        <v>292.6245033</v>
+        <v>289.32450345</v>
       </c>
       <c r="Q24">
-        <v>298.1945033</v>
+        <v>294.89450345</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07358710373594272</v>
+        <v>0.07391919405228337</v>
       </c>
       <c r="T24">
-        <v>0.5569552590353244</v>
+        <v>0.5636115644177878</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.030640724533256</v>
+        <v>4.81191721477094</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06836487942025819</v>
+        <v>0.06838241792648106</v>
       </c>
       <c r="C25">
-        <v>5158.80395410929</v>
+        <v>5090.408617807723</v>
       </c>
       <c r="D25">
-        <v>5822.01895410929</v>
+        <v>5819.928617807723</v>
       </c>
       <c r="E25">
-        <v>-361.5849999999998</v>
+        <v>-295.2799999999997</v>
       </c>
       <c r="F25">
-        <v>1525.015</v>
+        <v>1591.32</v>
       </c>
       <c r="G25">
         <v>861.8</v>
@@ -3343,28 +3343,28 @@
         <v>405.805</v>
       </c>
       <c r="M25">
-        <v>84.3333295</v>
+        <v>87.99999600000001</v>
       </c>
       <c r="N25">
-        <v>321.4716705</v>
+        <v>317.805004</v>
       </c>
       <c r="O25">
-        <v>32.14716705</v>
+        <v>31.7805004</v>
       </c>
       <c r="P25">
-        <v>289.32450345</v>
+        <v>286.0245036</v>
       </c>
       <c r="Q25">
-        <v>294.89450345</v>
+        <v>291.5945036</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07391919405228337</v>
+        <v>0.07426002358747508</v>
       </c>
       <c r="T25">
-        <v>0.5636115644177878</v>
+        <v>0.5704430357313688</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.81191721477094</v>
+        <v>4.611420664155484</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06838241792648106</v>
+        <v>0.06896245643270393</v>
       </c>
       <c r="C26">
-        <v>5090.408617807723</v>
+        <v>4955.807207279186</v>
       </c>
       <c r="D26">
-        <v>5819.928617807723</v>
+        <v>5751.632207279185</v>
       </c>
       <c r="E26">
-        <v>-295.28</v>
+        <v>-228.9749999999999</v>
       </c>
       <c r="F26">
-        <v>1591.32</v>
+        <v>1657.625</v>
       </c>
       <c r="G26">
         <v>861.8</v>
@@ -3425,45 +3425,45 @@
         <v>405.805</v>
       </c>
       <c r="M26">
-        <v>87.999996</v>
+        <v>95.81072500000001</v>
       </c>
       <c r="N26">
-        <v>317.805004</v>
+        <v>309.994275</v>
       </c>
       <c r="O26">
-        <v>31.7805004</v>
+        <v>30.9994275</v>
       </c>
       <c r="P26">
-        <v>286.0245036</v>
+        <v>278.9948475</v>
       </c>
       <c r="Q26">
-        <v>291.5945036</v>
+        <v>284.5648475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07426002358747508</v>
+        <v>0.07460994191027191</v>
       </c>
       <c r="T26">
-        <v>0.5704430357313688</v>
+        <v>0.5774566796133118</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.1</v>
       </c>
       <c r="W26">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.611420664155485</v>
+        <v>4.235486162953052</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06896245643270393</v>
+        <v>0.06900249493892679</v>
       </c>
       <c r="C27">
-        <v>4955.807207279186</v>
+        <v>4884.846981818982</v>
       </c>
       <c r="D27">
-        <v>5751.632207279185</v>
+        <v>5746.976981818982</v>
       </c>
       <c r="E27">
-        <v>-228.9749999999999</v>
+        <v>-162.6699999999998</v>
       </c>
       <c r="F27">
-        <v>1657.625</v>
+        <v>1723.93</v>
       </c>
       <c r="G27">
         <v>861.8</v>
@@ -3507,28 +3507,28 @@
         <v>405.805</v>
       </c>
       <c r="M27">
-        <v>95.81072500000001</v>
+        <v>99.64315400000001</v>
       </c>
       <c r="N27">
-        <v>309.994275</v>
+        <v>306.161846</v>
       </c>
       <c r="O27">
-        <v>30.9994275</v>
+        <v>30.6161846</v>
       </c>
       <c r="P27">
-        <v>278.9948475</v>
+        <v>275.5456614</v>
       </c>
       <c r="Q27">
-        <v>284.5648475</v>
+        <v>281.1156614</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07460994191027191</v>
+        <v>0.07496931748503621</v>
       </c>
       <c r="T27">
-        <v>0.5774566796133118</v>
+        <v>0.5846598814380102</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.235486162953052</v>
+        <v>4.072582848993318</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06900249493892679</v>
+        <v>0.06989303344514966</v>
       </c>
       <c r="C28">
-        <v>4884.846981818982</v>
+        <v>4716.913553290682</v>
       </c>
       <c r="D28">
-        <v>5746.976981818982</v>
+        <v>5645.348553290683</v>
       </c>
       <c r="E28">
-        <v>-162.6699999999998</v>
+        <v>-96.36499999999978</v>
       </c>
       <c r="F28">
-        <v>1723.93</v>
+        <v>1790.235</v>
       </c>
       <c r="G28">
         <v>861.8</v>
@@ -3589,45 +3589,45 @@
         <v>405.805</v>
       </c>
       <c r="M28">
-        <v>99.64315400000001</v>
+        <v>109.7414055</v>
       </c>
       <c r="N28">
-        <v>306.161846</v>
+        <v>296.0635945</v>
       </c>
       <c r="O28">
-        <v>30.6161846</v>
+        <v>29.60635945</v>
       </c>
       <c r="P28">
-        <v>275.5456614</v>
+        <v>266.45723505</v>
       </c>
       <c r="Q28">
-        <v>281.1156614</v>
+        <v>272.02723505</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07496931748503621</v>
+        <v>0.07533853896595845</v>
       </c>
       <c r="T28">
-        <v>0.5846598814380102</v>
+        <v>0.5920604312579056</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.1</v>
       </c>
       <c r="W28">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.072582848993318</v>
+        <v>3.697829439591057</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06989303344514966</v>
+        <v>0.06996457195137254</v>
       </c>
       <c r="C29">
-        <v>4716.913553290682</v>
+        <v>4642.600311631283</v>
       </c>
       <c r="D29">
-        <v>5645.348553290683</v>
+        <v>5637.340311631283</v>
       </c>
       <c r="E29">
-        <v>-96.36499999999978</v>
+        <v>-30.05999999999972</v>
       </c>
       <c r="F29">
-        <v>1790.235</v>
+        <v>1856.54</v>
       </c>
       <c r="G29">
         <v>861.8</v>
@@ -3671,28 +3671,28 @@
         <v>405.805</v>
       </c>
       <c r="M29">
-        <v>109.7414055</v>
+        <v>113.805902</v>
       </c>
       <c r="N29">
-        <v>296.0635945</v>
+        <v>291.999098</v>
       </c>
       <c r="O29">
-        <v>29.60635945</v>
+        <v>29.1999098</v>
       </c>
       <c r="P29">
-        <v>266.45723505</v>
+        <v>262.7991882</v>
       </c>
       <c r="Q29">
-        <v>272.02723505</v>
+        <v>268.3691882</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07533853896595845</v>
+        <v>0.07571801659912852</v>
       </c>
       <c r="T29">
-        <v>0.5920604312579056</v>
+        <v>0.5996665519061315</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.697829439591057</v>
+        <v>3.565764102462805</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06996457195137254</v>
+        <v>0.07076691045759539</v>
       </c>
       <c r="C30">
-        <v>4642.600311631283</v>
+        <v>4488.011050115199</v>
       </c>
       <c r="D30">
-        <v>5637.340311631283</v>
+        <v>5549.056050115199</v>
       </c>
       <c r="E30">
-        <v>-30.05999999999972</v>
+        <v>36.24500000000035</v>
       </c>
       <c r="F30">
-        <v>1856.54</v>
+        <v>1922.845</v>
       </c>
       <c r="G30">
         <v>861.8</v>
@@ -3753,45 +3753,45 @@
         <v>405.805</v>
       </c>
       <c r="M30">
-        <v>113.805902</v>
+        <v>123.2543645</v>
       </c>
       <c r="N30">
-        <v>291.999098</v>
+        <v>282.5506355</v>
       </c>
       <c r="O30">
-        <v>29.1999098</v>
+        <v>28.25506355</v>
       </c>
       <c r="P30">
-        <v>262.7991882</v>
+        <v>254.29557195</v>
       </c>
       <c r="Q30">
-        <v>268.3691882</v>
+        <v>259.86557195</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07571801659912852</v>
+        <v>0.07610818374309211</v>
       </c>
       <c r="T30">
-        <v>0.5996665519061315</v>
+        <v>0.6074869294740258</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.565764102462805</v>
+        <v>3.29241890659377</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07076691045759539</v>
+        <v>0.07086364896381826</v>
       </c>
       <c r="C31">
-        <v>4488.011050115199</v>
+        <v>4411.248002331103</v>
       </c>
       <c r="D31">
-        <v>5549.056050115199</v>
+        <v>5538.598002331102</v>
       </c>
       <c r="E31">
-        <v>36.24499999999989</v>
+        <v>102.55</v>
       </c>
       <c r="F31">
-        <v>1922.845</v>
+        <v>1989.15</v>
       </c>
       <c r="G31">
         <v>861.8</v>
@@ -3835,28 +3835,28 @@
         <v>405.805</v>
       </c>
       <c r="M31">
-        <v>123.2543645</v>
+        <v>127.504515</v>
       </c>
       <c r="N31">
-        <v>282.5506355</v>
+        <v>278.300485</v>
       </c>
       <c r="O31">
-        <v>28.25506355</v>
+        <v>27.8300485</v>
       </c>
       <c r="P31">
-        <v>254.29557195</v>
+        <v>250.4704365</v>
       </c>
       <c r="Q31">
-        <v>259.86557195</v>
+        <v>256.0404365</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07610818374309211</v>
+        <v>0.07650949851974038</v>
       </c>
       <c r="T31">
-        <v>0.6074869294740257</v>
+        <v>0.6155307464010027</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.29241890659377</v>
+        <v>3.182671609707311</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07086364896381826</v>
+        <v>0.07096038747004113</v>
       </c>
       <c r="C32">
-        <v>4411.248002331103</v>
+        <v>4334.524299986744</v>
       </c>
       <c r="D32">
-        <v>5538.598002331102</v>
+        <v>5528.179299986744</v>
       </c>
       <c r="E32">
-        <v>102.55</v>
+        <v>168.855</v>
       </c>
       <c r="F32">
-        <v>1989.15</v>
+        <v>2055.455</v>
       </c>
       <c r="G32">
         <v>861.8</v>
@@ -3917,28 +3917,28 @@
         <v>405.805</v>
       </c>
       <c r="M32">
-        <v>127.504515</v>
+        <v>131.7546655</v>
       </c>
       <c r="N32">
-        <v>278.300485</v>
+        <v>274.0503345</v>
       </c>
       <c r="O32">
-        <v>27.8300485</v>
+        <v>27.40503345</v>
       </c>
       <c r="P32">
-        <v>250.4704365</v>
+        <v>246.64530105</v>
       </c>
       <c r="Q32">
-        <v>256.0404365</v>
+        <v>252.21530105</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07650949851974038</v>
+        <v>0.07692244560875527</v>
       </c>
       <c r="T32">
-        <v>0.6155307464010027</v>
+        <v>0.6238077174418051</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.182671609707311</v>
+        <v>3.08000478358772</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07096038747004113</v>
+        <v>0.07330352597626399</v>
       </c>
       <c r="C33">
-        <v>4334.524299986744</v>
+        <v>4027.315149855997</v>
       </c>
       <c r="D33">
-        <v>5528.179299986744</v>
+        <v>5287.275149855997</v>
       </c>
       <c r="E33">
-        <v>168.855</v>
+        <v>235.1600000000003</v>
       </c>
       <c r="F33">
-        <v>2055.455</v>
+        <v>2121.76</v>
       </c>
       <c r="G33">
         <v>861.8</v>
@@ -3999,45 +3999,45 @@
         <v>405.805</v>
       </c>
       <c r="M33">
-        <v>131.7546655</v>
+        <v>152.554544</v>
       </c>
       <c r="N33">
-        <v>274.0503345</v>
+        <v>253.250456</v>
       </c>
       <c r="O33">
-        <v>27.40503345</v>
+        <v>25.3250456</v>
       </c>
       <c r="P33">
-        <v>246.64530105</v>
+        <v>227.9254104</v>
       </c>
       <c r="Q33">
-        <v>252.21530105</v>
+        <v>233.4954104</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07692244560875527</v>
+        <v>0.07734753820038824</v>
       </c>
       <c r="T33">
-        <v>0.6238077174418051</v>
+        <v>0.6323281288073369</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.1</v>
       </c>
       <c r="W33">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.08000478358772</v>
+        <v>2.660064979775364</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07330352597626399</v>
+        <v>0.07347046448248687</v>
       </c>
       <c r="C34">
-        <v>4027.315149855997</v>
+        <v>3944.645513227294</v>
       </c>
       <c r="D34">
-        <v>5287.275149855997</v>
+        <v>5270.910513227294</v>
       </c>
       <c r="E34">
-        <v>235.1600000000003</v>
+        <v>301.4650000000001</v>
       </c>
       <c r="F34">
-        <v>2121.76</v>
+        <v>2188.065</v>
       </c>
       <c r="G34">
         <v>861.8</v>
@@ -4081,28 +4081,28 @@
         <v>405.805</v>
       </c>
       <c r="M34">
-        <v>152.554544</v>
+        <v>157.3218735</v>
       </c>
       <c r="N34">
-        <v>253.250456</v>
+        <v>248.4831265</v>
       </c>
       <c r="O34">
-        <v>25.3250456</v>
+        <v>24.84831265</v>
       </c>
       <c r="P34">
-        <v>227.9254104</v>
+        <v>223.63481385</v>
       </c>
       <c r="Q34">
-        <v>233.4954104</v>
+        <v>229.20481385</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07734753820038824</v>
+        <v>0.07778532012311473</v>
       </c>
       <c r="T34">
-        <v>0.6323281288073369</v>
+        <v>0.6411028808106458</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.660064979775364</v>
+        <v>2.579456950085202</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07347046448248687</v>
+        <v>0.07363740298870974</v>
       </c>
       <c r="C35">
-        <v>3944.645513227294</v>
+        <v>3862.076864351444</v>
       </c>
       <c r="D35">
-        <v>5270.910513227294</v>
+        <v>5254.646864351444</v>
       </c>
       <c r="E35">
-        <v>301.4650000000001</v>
+        <v>367.7700000000004</v>
       </c>
       <c r="F35">
-        <v>2188.065</v>
+        <v>2254.37</v>
       </c>
       <c r="G35">
         <v>861.8</v>
@@ -4163,28 +4163,28 @@
         <v>405.805</v>
       </c>
       <c r="M35">
-        <v>157.3218735</v>
+        <v>162.089203</v>
       </c>
       <c r="N35">
-        <v>248.4831265</v>
+        <v>243.715797</v>
       </c>
       <c r="O35">
-        <v>24.84831265</v>
+        <v>24.3715797</v>
       </c>
       <c r="P35">
-        <v>223.63481385</v>
+        <v>219.3442173</v>
       </c>
       <c r="Q35">
-        <v>229.20481385</v>
+        <v>224.9142173</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07778532012311473</v>
+        <v>0.07823636816471173</v>
       </c>
       <c r="T35">
-        <v>0.6411028808106458</v>
+        <v>0.6501435343898126</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.579456950085202</v>
+        <v>2.503590569200343</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07363740298870974</v>
+        <v>0.0750328414949326</v>
       </c>
       <c r="C36">
-        <v>3862.076864351444</v>
+        <v>3663.651210141241</v>
       </c>
       <c r="D36">
-        <v>5254.646864351444</v>
+        <v>5122.526210141241</v>
       </c>
       <c r="E36">
-        <v>367.7700000000004</v>
+        <v>434.0750000000003</v>
       </c>
       <c r="F36">
-        <v>2254.37</v>
+        <v>2320.675</v>
       </c>
       <c r="G36">
         <v>861.8</v>
@@ -4245,45 +4245,45 @@
         <v>405.805</v>
       </c>
       <c r="M36">
-        <v>162.089203</v>
+        <v>175.907165</v>
       </c>
       <c r="N36">
-        <v>243.715797</v>
+        <v>229.897835</v>
       </c>
       <c r="O36">
-        <v>24.3715797</v>
+        <v>22.9897835</v>
       </c>
       <c r="P36">
-        <v>219.3442173</v>
+        <v>206.9080515</v>
       </c>
       <c r="Q36">
-        <v>224.9142173</v>
+        <v>212.4780515</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07823636816471173</v>
+        <v>0.07870129460758862</v>
       </c>
       <c r="T36">
-        <v>0.6501435343898126</v>
+        <v>0.6594623619252614</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.1</v>
       </c>
       <c r="W36">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.503590569200343</v>
+        <v>2.306927065762216</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0750328414949326</v>
+        <v>0.07523488000115547</v>
       </c>
       <c r="C37">
-        <v>3663.651210141241</v>
+        <v>3578.765740994263</v>
       </c>
       <c r="D37">
-        <v>5122.526210141241</v>
+        <v>5103.945740994263</v>
       </c>
       <c r="E37">
-        <v>434.0750000000003</v>
+        <v>500.3800000000006</v>
       </c>
       <c r="F37">
-        <v>2320.675</v>
+        <v>2386.98</v>
       </c>
       <c r="G37">
         <v>861.8</v>
@@ -4327,28 +4327,28 @@
         <v>405.805</v>
       </c>
       <c r="M37">
-        <v>175.907165</v>
+        <v>180.9330840000001</v>
       </c>
       <c r="N37">
-        <v>229.897835</v>
+        <v>224.8719159999999</v>
       </c>
       <c r="O37">
-        <v>22.9897835</v>
+        <v>22.4871916</v>
       </c>
       <c r="P37">
-        <v>206.9080515</v>
+        <v>202.3847244</v>
       </c>
       <c r="Q37">
-        <v>212.4780515</v>
+        <v>207.9547243999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07870129460758862</v>
+        <v>0.07918075000180544</v>
       </c>
       <c r="T37">
-        <v>0.6594623619252614</v>
+        <v>0.6690724028211931</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.306927065762216</v>
+        <v>2.242845758379931</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07523488000115548</v>
+        <v>0.07543691850737834</v>
       </c>
       <c r="C38">
-        <v>3578.765740994262</v>
+        <v>3494.014575161828</v>
       </c>
       <c r="D38">
-        <v>5103.945740994262</v>
+        <v>5085.499575161828</v>
       </c>
       <c r="E38">
-        <v>500.3800000000001</v>
+        <v>566.6849999999999</v>
       </c>
       <c r="F38">
-        <v>2386.98</v>
+        <v>2453.285</v>
       </c>
       <c r="G38">
         <v>861.8</v>
@@ -4409,28 +4409,28 @@
         <v>405.805</v>
       </c>
       <c r="M38">
-        <v>180.933084</v>
+        <v>185.959003</v>
       </c>
       <c r="N38">
-        <v>224.871916</v>
+        <v>219.845997</v>
       </c>
       <c r="O38">
-        <v>22.4871916</v>
+        <v>21.9845997</v>
       </c>
       <c r="P38">
-        <v>202.3847244</v>
+        <v>197.8613973</v>
       </c>
       <c r="Q38">
-        <v>207.9547244</v>
+        <v>203.4313973</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07918075000180544</v>
+        <v>0.07967542620218784</v>
       </c>
       <c r="T38">
-        <v>0.6690724028211931</v>
+        <v>0.6789875243804875</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.242845758379932</v>
+        <v>2.182228305450745</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07543691850737834</v>
+        <v>0.07563895701360121</v>
       </c>
       <c r="C39">
-        <v>3494.014575161828</v>
+        <v>3409.396261731203</v>
       </c>
       <c r="D39">
-        <v>5085.499575161828</v>
+        <v>5067.186261731203</v>
       </c>
       <c r="E39">
-        <v>566.6849999999999</v>
+        <v>632.9900000000002</v>
       </c>
       <c r="F39">
-        <v>2453.285</v>
+        <v>2519.59</v>
       </c>
       <c r="G39">
         <v>861.8</v>
@@ -4491,28 +4491,28 @@
         <v>405.805</v>
       </c>
       <c r="M39">
-        <v>185.959003</v>
+        <v>190.984922</v>
       </c>
       <c r="N39">
-        <v>219.845997</v>
+        <v>214.820078</v>
       </c>
       <c r="O39">
-        <v>21.9845997</v>
+        <v>21.4820078</v>
       </c>
       <c r="P39">
-        <v>197.8613973</v>
+        <v>193.3380702</v>
       </c>
       <c r="Q39">
-        <v>203.4313973</v>
+        <v>198.9080702</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07967542620218784</v>
+        <v>0.0801860596993568</v>
       </c>
       <c r="T39">
-        <v>0.6789875243804875</v>
+        <v>0.6892224885707271</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.182228305450745</v>
+        <v>2.124801244780988</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07563895701360121</v>
+        <v>0.07584099551982408</v>
       </c>
       <c r="C40">
-        <v>3409.396261731203</v>
+        <v>3324.909370614102</v>
       </c>
       <c r="D40">
-        <v>5067.186261731203</v>
+        <v>5049.004370614102</v>
       </c>
       <c r="E40">
-        <v>632.9900000000002</v>
+        <v>699.2950000000001</v>
       </c>
       <c r="F40">
-        <v>2519.59</v>
+        <v>2585.895</v>
       </c>
       <c r="G40">
         <v>861.8</v>
@@ -4573,28 +4573,28 @@
         <v>405.805</v>
       </c>
       <c r="M40">
-        <v>190.984922</v>
+        <v>196.010841</v>
       </c>
       <c r="N40">
-        <v>214.820078</v>
+        <v>209.794159</v>
       </c>
       <c r="O40">
-        <v>21.4820078</v>
+        <v>20.9794159</v>
       </c>
       <c r="P40">
-        <v>193.3380702</v>
+        <v>188.8147431</v>
       </c>
       <c r="Q40">
-        <v>198.9080702</v>
+        <v>194.3847431</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0801860596993568</v>
+        <v>0.08071343527840014</v>
       </c>
       <c r="T40">
-        <v>0.6892224885707271</v>
+        <v>0.6997930253573678</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.124801244780988</v>
+        <v>2.070319161581476</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07584099551982408</v>
+        <v>0.07604303402604695</v>
       </c>
       <c r="C41">
-        <v>3324.909370614102</v>
+        <v>3240.552492174417</v>
       </c>
       <c r="D41">
-        <v>5049.004370614102</v>
+        <v>5030.952492174417</v>
       </c>
       <c r="E41">
-        <v>699.2950000000001</v>
+        <v>765.6000000000004</v>
       </c>
       <c r="F41">
-        <v>2585.895</v>
+        <v>2652.2</v>
       </c>
       <c r="G41">
         <v>861.8</v>
@@ -4655,28 +4655,28 @@
         <v>405.805</v>
       </c>
       <c r="M41">
-        <v>196.010841</v>
+        <v>201.03676</v>
       </c>
       <c r="N41">
-        <v>209.794159</v>
+        <v>204.76824</v>
       </c>
       <c r="O41">
-        <v>20.9794159</v>
+        <v>20.476824</v>
       </c>
       <c r="P41">
-        <v>188.8147431</v>
+        <v>184.291416</v>
       </c>
       <c r="Q41">
-        <v>194.3847431</v>
+        <v>189.861416</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08071343527840014</v>
+        <v>0.08125839004341158</v>
       </c>
       <c r="T41">
-        <v>0.6997930253573678</v>
+        <v>0.71071591337023</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.070319161581476</v>
+        <v>2.018561182541939</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07604303402604695</v>
+        <v>0.08148487253226981</v>
       </c>
       <c r="C42">
-        <v>3240.552492174417</v>
+        <v>2732.322266538368</v>
       </c>
       <c r="D42">
-        <v>5030.952492174417</v>
+        <v>4589.027266538368</v>
       </c>
       <c r="E42">
-        <v>765.6000000000004</v>
+        <v>831.9050000000002</v>
       </c>
       <c r="F42">
-        <v>2652.2</v>
+        <v>2718.505</v>
       </c>
       <c r="G42">
         <v>861.8</v>
@@ -4737,45 +4737,45 @@
         <v>405.805</v>
       </c>
       <c r="M42">
-        <v>201.03676</v>
+        <v>244.66545</v>
       </c>
       <c r="N42">
-        <v>204.76824</v>
+        <v>161.13955</v>
       </c>
       <c r="O42">
-        <v>20.476824</v>
+        <v>16.113955</v>
       </c>
       <c r="P42">
-        <v>184.291416</v>
+        <v>145.025595</v>
       </c>
       <c r="Q42">
-        <v>189.861416</v>
+        <v>150.595595</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08125839004341158</v>
+        <v>0.08182181785130477</v>
       </c>
       <c r="T42">
-        <v>0.71071591337023</v>
+        <v>0.7220090687733586</v>
       </c>
       <c r="U42">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V42">
         <v>0.1</v>
       </c>
       <c r="W42">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.018561182541939</v>
+        <v>1.658611790099501</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08148487253226981</v>
+        <v>0.08181471103849268</v>
       </c>
       <c r="C43">
-        <v>2732.322266538368</v>
+        <v>2641.713768693662</v>
       </c>
       <c r="D43">
-        <v>4589.027266538368</v>
+        <v>4564.723768693662</v>
       </c>
       <c r="E43">
-        <v>831.9050000000002</v>
+        <v>898.2100000000005</v>
       </c>
       <c r="F43">
-        <v>2718.505</v>
+        <v>2784.81</v>
       </c>
       <c r="G43">
         <v>861.8</v>
@@ -4819,28 +4819,28 @@
         <v>405.805</v>
       </c>
       <c r="M43">
-        <v>244.66545</v>
+        <v>250.6329</v>
       </c>
       <c r="N43">
-        <v>161.13955</v>
+        <v>155.1721</v>
       </c>
       <c r="O43">
-        <v>16.113955</v>
+        <v>15.51721</v>
       </c>
       <c r="P43">
-        <v>145.025595</v>
+        <v>139.65489</v>
       </c>
       <c r="Q43">
-        <v>150.595595</v>
+        <v>145.22489</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08182181785130477</v>
+        <v>0.08240467420429773</v>
       </c>
       <c r="T43">
-        <v>0.7220090687733586</v>
+        <v>0.7336916433283193</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.658611790099501</v>
+        <v>1.61912103319237</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08181471103849269</v>
+        <v>0.08214454954471556</v>
       </c>
       <c r="C44">
-        <v>2641.713768693662</v>
+        <v>2551.361337468782</v>
       </c>
       <c r="D44">
-        <v>4564.723768693661</v>
+        <v>4540.676337468782</v>
       </c>
       <c r="E44">
-        <v>898.21</v>
+        <v>964.5149999999999</v>
       </c>
       <c r="F44">
-        <v>2784.81</v>
+        <v>2851.115</v>
       </c>
       <c r="G44">
         <v>861.8</v>
@@ -4901,28 +4901,28 @@
         <v>405.805</v>
       </c>
       <c r="M44">
-        <v>250.6329</v>
+        <v>256.60035</v>
       </c>
       <c r="N44">
-        <v>155.1721</v>
+        <v>149.20465</v>
       </c>
       <c r="O44">
-        <v>15.51721</v>
+        <v>14.920465</v>
       </c>
       <c r="P44">
-        <v>139.65489</v>
+        <v>134.284185</v>
       </c>
       <c r="Q44">
-        <v>145.22489</v>
+        <v>139.854185</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08240467420429773</v>
+        <v>0.0830079816573957</v>
       </c>
       <c r="T44">
-        <v>0.7336916433283192</v>
+        <v>0.7457841327799452</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.61912103319237</v>
+        <v>1.581467055676269</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08214454954471556</v>
+        <v>0.08247438805093843</v>
       </c>
       <c r="C45">
-        <v>2551.361337468782</v>
+        <v>2461.260947116423</v>
       </c>
       <c r="D45">
-        <v>4540.676337468782</v>
+        <v>4516.880947116423</v>
       </c>
       <c r="E45">
-        <v>964.5149999999999</v>
+        <v>1030.82</v>
       </c>
       <c r="F45">
-        <v>2851.115</v>
+        <v>2917.42</v>
       </c>
       <c r="G45">
         <v>861.8</v>
@@ -4983,28 +4983,28 @@
         <v>405.805</v>
       </c>
       <c r="M45">
-        <v>256.60035</v>
+        <v>262.5678</v>
       </c>
       <c r="N45">
-        <v>149.20465</v>
+        <v>143.2372</v>
       </c>
       <c r="O45">
-        <v>14.920465</v>
+        <v>14.32372</v>
       </c>
       <c r="P45">
-        <v>134.284185</v>
+        <v>128.91348</v>
       </c>
       <c r="Q45">
-        <v>139.854185</v>
+        <v>134.48348</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0830079816573957</v>
+        <v>0.08363283580524718</v>
       </c>
       <c r="T45">
-        <v>0.7457841327799452</v>
+        <v>0.7583084968548436</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.581467055676269</v>
+        <v>1.545524622592717</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08247438805093843</v>
+        <v>0.0828042265571613</v>
       </c>
       <c r="C46">
-        <v>2461.260947116423</v>
+        <v>2371.408655836987</v>
       </c>
       <c r="D46">
-        <v>4516.880947116423</v>
+        <v>4493.333655836987</v>
       </c>
       <c r="E46">
-        <v>1030.82</v>
+        <v>1097.125</v>
       </c>
       <c r="F46">
-        <v>2917.42</v>
+        <v>2983.725</v>
       </c>
       <c r="G46">
         <v>861.8</v>
@@ -5065,28 +5065,28 @@
         <v>405.805</v>
       </c>
       <c r="M46">
-        <v>262.5678</v>
+        <v>268.53525</v>
       </c>
       <c r="N46">
-        <v>143.2372</v>
+        <v>137.26975</v>
       </c>
       <c r="O46">
-        <v>14.32372</v>
+        <v>13.726975</v>
       </c>
       <c r="P46">
-        <v>128.91348</v>
+        <v>123.542775</v>
       </c>
       <c r="Q46">
-        <v>134.48348</v>
+        <v>129.112775</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08363283580524718</v>
+        <v>0.08428041192211143</v>
       </c>
       <c r="T46">
-        <v>0.7583084968548436</v>
+        <v>0.7712882923506472</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.545524622592717</v>
+        <v>1.511179630979546</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0828042265571613</v>
+        <v>0.1073772755914762</v>
       </c>
       <c r="C47">
-        <v>2371.408655836987</v>
+        <v>1048.149483605231</v>
       </c>
       <c r="D47">
-        <v>4493.333655836987</v>
+        <v>3236.379483605231</v>
       </c>
       <c r="E47">
-        <v>1097.125</v>
+        <v>1163.43</v>
       </c>
       <c r="F47">
-        <v>2983.725</v>
+        <v>3050.03</v>
       </c>
       <c r="G47">
         <v>861.8</v>
@@ -5147,45 +5147,45 @@
         <v>405.805</v>
       </c>
       <c r="M47">
-        <v>268.53525</v>
+        <v>447.7444040000001</v>
       </c>
       <c r="N47">
-        <v>137.26975</v>
+        <v>-41.93940400000008</v>
       </c>
       <c r="O47">
-        <v>13.726975</v>
+        <v>-4.193940400000009</v>
       </c>
       <c r="P47">
-        <v>123.542775</v>
+        <v>-37.74546360000007</v>
       </c>
       <c r="Q47">
-        <v>129.112775</v>
+        <v>-32.17546360000007</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08428041192211143</v>
+        <v>0.08512880203137652</v>
       </c>
       <c r="T47">
-        <v>0.7712882923506472</v>
+        <v>0.7882931352288038</v>
       </c>
       <c r="U47">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1</v>
+        <v>0.09063318187221832</v>
       </c>
       <c r="W47">
-        <v>0.081</v>
+        <v>0.1334950489011583</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.511179630979546</v>
+        <v>0.9063318187221832</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1073772755914762</v>
+        <v>0.1083872755914762</v>
       </c>
       <c r="C48">
-        <v>1048.149483605231</v>
+        <v>945.0563616669087</v>
       </c>
       <c r="D48">
-        <v>3236.379483605231</v>
+        <v>3199.591361666909</v>
       </c>
       <c r="E48">
-        <v>1163.43</v>
+        <v>1229.735</v>
       </c>
       <c r="F48">
-        <v>3050.03</v>
+        <v>3116.335</v>
       </c>
       <c r="G48">
         <v>861.8</v>
@@ -5229,37 +5229,37 @@
         <v>405.805</v>
       </c>
       <c r="M48">
-        <v>447.7444040000001</v>
+        <v>457.4779780000001</v>
       </c>
       <c r="N48">
-        <v>-41.93940400000008</v>
+        <v>-51.67297800000006</v>
       </c>
       <c r="O48">
-        <v>-4.193940400000009</v>
+        <v>-5.167297800000006</v>
       </c>
       <c r="P48">
-        <v>-37.74546360000007</v>
+        <v>-46.50568020000005</v>
       </c>
       <c r="Q48">
-        <v>-32.17546360000007</v>
+        <v>-40.93568020000005</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08512880203137652</v>
+        <v>0.08587085489989306</v>
       </c>
       <c r="T48">
-        <v>0.7882931352288038</v>
+        <v>0.8031665906104795</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.09063318187221832</v>
+        <v>0.088704816300469</v>
       </c>
       <c r="W48">
-        <v>0.1334950489011583</v>
+        <v>0.1337781329670912</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9063318187221832</v>
+        <v>0.8870481630046899</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1083872755914762</v>
+        <v>0.1093972755914762</v>
       </c>
       <c r="C49">
-        <v>945.0563616669087</v>
+        <v>842.7901854147494</v>
       </c>
       <c r="D49">
-        <v>3199.591361666909</v>
+        <v>3163.63018541475</v>
       </c>
       <c r="E49">
-        <v>1229.735</v>
+        <v>1296.04</v>
       </c>
       <c r="F49">
-        <v>3116.335</v>
+        <v>3182.64</v>
       </c>
       <c r="G49">
         <v>861.8</v>
@@ -5311,37 +5311,37 @@
         <v>405.805</v>
       </c>
       <c r="M49">
-        <v>457.4779780000001</v>
+        <v>467.2115520000001</v>
       </c>
       <c r="N49">
-        <v>-51.67297800000006</v>
+        <v>-61.40655200000009</v>
       </c>
       <c r="O49">
-        <v>-5.167297800000006</v>
+        <v>-6.140655200000009</v>
       </c>
       <c r="P49">
-        <v>-46.50568020000005</v>
+        <v>-55.26589680000008</v>
       </c>
       <c r="Q49">
-        <v>-40.93568020000005</v>
+        <v>-49.69589680000008</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08587085489989306</v>
+        <v>0.08664144826335254</v>
       </c>
       <c r="T49">
-        <v>0.8031665906104795</v>
+        <v>0.8186121019683734</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.088704816300469</v>
+        <v>0.08685679929420922</v>
       </c>
       <c r="W49">
-        <v>0.1337781329670912</v>
+        <v>0.1340494218636101</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8870481630046899</v>
+        <v>0.8685679929420922</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1093972755914762</v>
+        <v>0.1104072755914762</v>
       </c>
       <c r="C50">
-        <v>842.7901854147499</v>
+        <v>741.3233818708281</v>
       </c>
       <c r="D50">
-        <v>3163.63018541475</v>
+        <v>3128.468381870828</v>
       </c>
       <c r="E50">
-        <v>1296.04</v>
+        <v>1362.345</v>
       </c>
       <c r="F50">
-        <v>3182.64</v>
+        <v>3248.945</v>
       </c>
       <c r="G50">
         <v>861.8</v>
@@ -5393,37 +5393,37 @@
         <v>405.805</v>
       </c>
       <c r="M50">
-        <v>467.211552</v>
+        <v>476.9451260000001</v>
       </c>
       <c r="N50">
-        <v>-61.40655200000003</v>
+        <v>-71.14012600000007</v>
       </c>
       <c r="O50">
-        <v>-6.140655200000004</v>
+        <v>-7.114012600000007</v>
       </c>
       <c r="P50">
-        <v>-55.26589680000003</v>
+        <v>-64.02611340000006</v>
       </c>
       <c r="Q50">
-        <v>-49.69589680000003</v>
+        <v>-58.45611340000006</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08664144826335254</v>
+        <v>0.08744226097439867</v>
       </c>
       <c r="T50">
-        <v>0.8186121019683733</v>
+        <v>0.8346633196540277</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.08685679929420924</v>
+        <v>0.08508421155351108</v>
       </c>
       <c r="W50">
-        <v>0.1340494218636101</v>
+        <v>0.1343096377439446</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8685679929420922</v>
+        <v>0.8508421155351107</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1104072755914762</v>
+        <v>0.1114172755914762</v>
       </c>
       <c r="C51">
-        <v>741.3233818708281</v>
+        <v>640.6295904094231</v>
       </c>
       <c r="D51">
-        <v>3128.468381870828</v>
+        <v>3094.079590409423</v>
       </c>
       <c r="E51">
-        <v>1362.345</v>
+        <v>1428.65</v>
       </c>
       <c r="F51">
-        <v>3248.945</v>
+        <v>3315.25</v>
       </c>
       <c r="G51">
         <v>861.8</v>
@@ -5475,37 +5475,37 @@
         <v>405.805</v>
       </c>
       <c r="M51">
-        <v>476.9451260000001</v>
+        <v>486.6787</v>
       </c>
       <c r="N51">
-        <v>-71.14012600000007</v>
+        <v>-80.87370000000004</v>
       </c>
       <c r="O51">
-        <v>-7.114012600000007</v>
+        <v>-8.087370000000005</v>
       </c>
       <c r="P51">
-        <v>-64.02611340000006</v>
+        <v>-72.78633000000004</v>
       </c>
       <c r="Q51">
-        <v>-58.45611340000006</v>
+        <v>-67.21633000000003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08744226097439867</v>
+        <v>0.08827510619388665</v>
       </c>
       <c r="T51">
-        <v>0.8346633196540277</v>
+        <v>0.8513565860471082</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.08508421155351108</v>
+        <v>0.08338252732244086</v>
       </c>
       <c r="W51">
-        <v>0.1343096377439446</v>
+        <v>0.1345594449890657</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8508421155351107</v>
+        <v>0.8338252732244086</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1114172755914762</v>
+        <v>0.1124272755914762</v>
       </c>
       <c r="C52">
-        <v>640.6295904094231</v>
+        <v>540.6835968493256</v>
       </c>
       <c r="D52">
-        <v>3094.079590409423</v>
+        <v>3060.438596849326</v>
       </c>
       <c r="E52">
-        <v>1428.65</v>
+        <v>1494.955</v>
       </c>
       <c r="F52">
-        <v>3315.25</v>
+        <v>3381.555</v>
       </c>
       <c r="G52">
         <v>861.8</v>
@@ -5557,37 +5557,37 @@
         <v>405.805</v>
       </c>
       <c r="M52">
-        <v>486.6787</v>
+        <v>496.412274</v>
       </c>
       <c r="N52">
-        <v>-80.87370000000004</v>
+        <v>-90.60727400000002</v>
       </c>
       <c r="O52">
-        <v>-8.087370000000005</v>
+        <v>-9.060727400000003</v>
       </c>
       <c r="P52">
-        <v>-72.78633000000004</v>
+        <v>-81.54654660000001</v>
       </c>
       <c r="Q52">
-        <v>-67.21633000000003</v>
+        <v>-75.97654660000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08827510619388665</v>
+        <v>0.0891419450958027</v>
       </c>
       <c r="T52">
-        <v>0.8513565860471082</v>
+        <v>0.8687312102521513</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.08338252732244086</v>
+        <v>0.08174757580631457</v>
       </c>
       <c r="W52">
-        <v>0.1345594449890657</v>
+        <v>0.134799455871633</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8338252732244086</v>
+        <v>0.8174757580631457</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1124272755914762</v>
+        <v>0.1134372755914761</v>
       </c>
       <c r="C53">
-        <v>540.6835968493256</v>
+        <v>441.4612717994592</v>
       </c>
       <c r="D53">
-        <v>3060.438596849326</v>
+        <v>3027.52127179946</v>
       </c>
       <c r="E53">
-        <v>1494.955</v>
+        <v>1561.26</v>
       </c>
       <c r="F53">
-        <v>3381.555</v>
+        <v>3447.86</v>
       </c>
       <c r="G53">
         <v>861.8</v>
@@ -5639,37 +5639,37 @@
         <v>405.805</v>
       </c>
       <c r="M53">
-        <v>496.412274</v>
+        <v>506.1458480000001</v>
       </c>
       <c r="N53">
-        <v>-90.60727400000002</v>
+        <v>-100.3408480000001</v>
       </c>
       <c r="O53">
-        <v>-9.060727400000003</v>
+        <v>-10.03408480000001</v>
       </c>
       <c r="P53">
-        <v>-81.54654660000001</v>
+        <v>-90.30676320000005</v>
       </c>
       <c r="Q53">
-        <v>-75.97654660000001</v>
+        <v>-84.73676320000004</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0891419450958027</v>
+        <v>0.09004490228529859</v>
       </c>
       <c r="T53">
-        <v>0.8687312102521513</v>
+        <v>0.8868297771324044</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.08174757580631457</v>
+        <v>0.08017550704080852</v>
       </c>
       <c r="W53">
-        <v>0.134799455871633</v>
+        <v>0.1350302355664093</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8174757580631457</v>
+        <v>0.8017550704080851</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1134372755914761</v>
+        <v>0.1433157456947142</v>
       </c>
       <c r="C54">
-        <v>441.4612717994592</v>
+        <v>-355.6279017466695</v>
       </c>
       <c r="D54">
-        <v>3027.52127179946</v>
+        <v>2296.737098253331</v>
       </c>
       <c r="E54">
-        <v>1561.26</v>
+        <v>1627.565</v>
       </c>
       <c r="F54">
-        <v>3447.86</v>
+        <v>3514.165</v>
       </c>
       <c r="G54">
         <v>861.8</v>
@@ -5721,45 +5721,45 @@
         <v>405.805</v>
       </c>
       <c r="M54">
-        <v>506.1458480000001</v>
+        <v>705.644332</v>
       </c>
       <c r="N54">
-        <v>-100.3408480000001</v>
+        <v>-299.839332</v>
       </c>
       <c r="O54">
-        <v>-10.03408480000001</v>
+        <v>-29.9839332</v>
       </c>
       <c r="P54">
-        <v>-90.30676320000005</v>
+        <v>-269.8553988</v>
       </c>
       <c r="Q54">
-        <v>-84.73676320000004</v>
+        <v>-264.2853988</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09004490228529859</v>
+        <v>0.09151494297910931</v>
       </c>
       <c r="T54">
-        <v>0.8868297771324044</v>
+        <v>0.9162947729518417</v>
       </c>
       <c r="U54">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.08017550704080852</v>
+        <v>0.05750843329951101</v>
       </c>
       <c r="W54">
-        <v>0.1350302355664093</v>
+        <v>0.1892523065934582</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8017550704080851</v>
+        <v>0.5750843329951101</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1433157456947142</v>
+        <v>0.1448657456947142</v>
       </c>
       <c r="C55">
-        <v>-355.6279017466695</v>
+        <v>-450.3370695623871</v>
       </c>
       <c r="D55">
-        <v>2296.737098253331</v>
+        <v>2268.332930437613</v>
       </c>
       <c r="E55">
-        <v>1627.565</v>
+        <v>1693.87</v>
       </c>
       <c r="F55">
-        <v>3514.165</v>
+        <v>3580.47</v>
       </c>
       <c r="G55">
         <v>861.8</v>
@@ -5803,37 +5803,37 @@
         <v>405.805</v>
       </c>
       <c r="M55">
-        <v>705.644332</v>
+        <v>718.958376</v>
       </c>
       <c r="N55">
-        <v>-299.839332</v>
+        <v>-313.153376</v>
       </c>
       <c r="O55">
-        <v>-29.9839332</v>
+        <v>-31.31533760000001</v>
       </c>
       <c r="P55">
-        <v>-269.8553988</v>
+        <v>-281.8380384</v>
       </c>
       <c r="Q55">
-        <v>-264.2853988</v>
+        <v>-276.2680384</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09151494297910931</v>
+        <v>0.09250874608735082</v>
       </c>
       <c r="T55">
-        <v>0.9162947729518417</v>
+        <v>0.9362142245377513</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.05750843329951101</v>
+        <v>0.05644346231248302</v>
       </c>
       <c r="W55">
-        <v>0.1892523065934582</v>
+        <v>0.1894661527676534</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5750843329951101</v>
+        <v>0.5644346231248303</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1448657456947142</v>
+        <v>0.1464157456947142</v>
       </c>
       <c r="C56">
-        <v>-450.3370695623871</v>
+        <v>-544.3522608347625</v>
       </c>
       <c r="D56">
-        <v>2268.332930437613</v>
+        <v>2240.622739165237</v>
       </c>
       <c r="E56">
-        <v>1693.87</v>
+        <v>1760.175</v>
       </c>
       <c r="F56">
-        <v>3580.47</v>
+        <v>3646.775</v>
       </c>
       <c r="G56">
         <v>861.8</v>
@@ -5885,37 +5885,37 @@
         <v>405.805</v>
       </c>
       <c r="M56">
-        <v>718.958376</v>
+        <v>732.27242</v>
       </c>
       <c r="N56">
-        <v>-313.153376</v>
+        <v>-326.46742</v>
       </c>
       <c r="O56">
-        <v>-31.31533760000001</v>
+        <v>-32.646742</v>
       </c>
       <c r="P56">
-        <v>-281.8380384</v>
+        <v>-293.820678</v>
       </c>
       <c r="Q56">
-        <v>-276.2680384</v>
+        <v>-288.250678</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09250874608735082</v>
+        <v>0.09354671822262528</v>
       </c>
       <c r="T56">
-        <v>0.9362142245377513</v>
+        <v>0.9570189850830347</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.05644346231248302</v>
+        <v>0.05541721754316516</v>
       </c>
       <c r="W56">
-        <v>0.1894661527676534</v>
+        <v>0.1896722227173324</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5644346231248303</v>
+        <v>0.5541721754316515</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1464157456947142</v>
+        <v>0.1479657456947142</v>
       </c>
       <c r="C57">
-        <v>-544.3522608347625</v>
+        <v>-637.6986016895748</v>
       </c>
       <c r="D57">
-        <v>2240.622739165237</v>
+        <v>2213.581398310426</v>
       </c>
       <c r="E57">
-        <v>1760.175</v>
+        <v>1826.48</v>
       </c>
       <c r="F57">
-        <v>3646.775</v>
+        <v>3713.08</v>
       </c>
       <c r="G57">
         <v>861.8</v>
@@ -5967,37 +5967,37 @@
         <v>405.805</v>
       </c>
       <c r="M57">
-        <v>732.27242</v>
+        <v>745.5864640000001</v>
       </c>
       <c r="N57">
-        <v>-326.46742</v>
+        <v>-339.7814640000001</v>
       </c>
       <c r="O57">
-        <v>-32.646742</v>
+        <v>-33.97814640000001</v>
       </c>
       <c r="P57">
-        <v>-293.820678</v>
+        <v>-305.8033176000001</v>
       </c>
       <c r="Q57">
-        <v>-288.250678</v>
+        <v>-300.2333176000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09354671822262528</v>
+        <v>0.09463187090950312</v>
       </c>
       <c r="T57">
-        <v>0.9570189850830347</v>
+        <v>0.9787694165621944</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.05541721754316516</v>
+        <v>0.05442762437275148</v>
       </c>
       <c r="W57">
-        <v>0.1896722227173324</v>
+        <v>0.1898709330259515</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5541721754316515</v>
+        <v>0.5442762437275148</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1479657456947142</v>
+        <v>0.1495157456947142</v>
       </c>
       <c r="C58">
-        <v>-637.6986016895748</v>
+        <v>-730.4000197609203</v>
       </c>
       <c r="D58">
-        <v>2213.581398310426</v>
+        <v>2187.18498023908</v>
       </c>
       <c r="E58">
-        <v>1826.48</v>
+        <v>1892.785</v>
       </c>
       <c r="F58">
-        <v>3713.08</v>
+        <v>3779.385</v>
       </c>
       <c r="G58">
         <v>861.8</v>
@@ -6049,37 +6049,37 @@
         <v>405.805</v>
       </c>
       <c r="M58">
-        <v>745.5864640000001</v>
+        <v>758.9005080000001</v>
       </c>
       <c r="N58">
-        <v>-339.7814640000001</v>
+        <v>-353.0955080000001</v>
       </c>
       <c r="O58">
-        <v>-33.97814640000001</v>
+        <v>-35.3095508</v>
       </c>
       <c r="P58">
-        <v>-305.8033176000001</v>
+        <v>-317.7859572</v>
       </c>
       <c r="Q58">
-        <v>-300.2333176000001</v>
+        <v>-312.2159572</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09463187090950312</v>
+        <v>0.0957674958143753</v>
       </c>
       <c r="T58">
-        <v>0.9787694165621944</v>
+        <v>1.001531496017129</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.05442762437275148</v>
+        <v>0.05347275376972076</v>
       </c>
       <c r="W58">
-        <v>0.1898709330259515</v>
+        <v>0.1900626710430401</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5442762437275148</v>
+        <v>0.5347275376972076</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1495157456947142</v>
+        <v>0.1510657456947143</v>
       </c>
       <c r="C59">
-        <v>-730.4000197609203</v>
+        <v>-822.4793148077424</v>
       </c>
       <c r="D59">
-        <v>2187.18498023908</v>
+        <v>2161.410685192258</v>
       </c>
       <c r="E59">
-        <v>1892.785</v>
+        <v>1959.090000000001</v>
       </c>
       <c r="F59">
-        <v>3779.385</v>
+        <v>3845.690000000001</v>
       </c>
       <c r="G59">
         <v>861.8</v>
@@ -6131,37 +6131,37 @@
         <v>405.805</v>
       </c>
       <c r="M59">
-        <v>758.9005080000001</v>
+        <v>772.2145520000001</v>
       </c>
       <c r="N59">
-        <v>-353.0955080000001</v>
+        <v>-366.4095520000001</v>
       </c>
       <c r="O59">
-        <v>-35.3095508</v>
+        <v>-36.64095520000001</v>
       </c>
       <c r="P59">
-        <v>-317.7859572</v>
+        <v>-329.7685968000001</v>
       </c>
       <c r="Q59">
-        <v>-312.2159572</v>
+        <v>-324.1985968000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.0957674958143753</v>
+        <v>0.09695719809566997</v>
       </c>
       <c r="T59">
-        <v>1.001531496017129</v>
+        <v>1.025377484017537</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.05347275376972076</v>
+        <v>0.05255080973920833</v>
       </c>
       <c r="W59">
-        <v>0.1900626710430401</v>
+        <v>0.190247797404367</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5347275376972076</v>
+        <v>0.5255080973920833</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1510657456947142</v>
+        <v>0.1526157456947142</v>
       </c>
       <c r="C60">
-        <v>-822.4793148077397</v>
+        <v>-913.9582243955256</v>
       </c>
       <c r="D60">
-        <v>2161.41068519226</v>
+        <v>2136.236775604474</v>
       </c>
       <c r="E60">
-        <v>1959.09</v>
+        <v>2025.395</v>
       </c>
       <c r="F60">
-        <v>3845.69</v>
+        <v>3911.995</v>
       </c>
       <c r="G60">
         <v>861.8</v>
@@ -6213,37 +6213,37 @@
         <v>405.805</v>
       </c>
       <c r="M60">
-        <v>772.2145519999999</v>
+        <v>785.528596</v>
       </c>
       <c r="N60">
-        <v>-366.4095519999999</v>
+        <v>-379.723596</v>
       </c>
       <c r="O60">
-        <v>-36.64095519999999</v>
+        <v>-37.9723596</v>
       </c>
       <c r="P60">
-        <v>-329.7685967999999</v>
+        <v>-341.7512364</v>
       </c>
       <c r="Q60">
-        <v>-324.1985967999999</v>
+        <v>-336.1812364</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09695719809566994</v>
+        <v>0.09820493463458871</v>
       </c>
       <c r="T60">
-        <v>1.025377484017537</v>
+        <v>1.050386690944794</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.05255080973920834</v>
+        <v>0.05166011804871328</v>
       </c>
       <c r="W60">
-        <v>0.190247797404367</v>
+        <v>0.1904266482958184</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5255080973920834</v>
+        <v>0.5166011804871328</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1526157456947142</v>
+        <v>0.1541657456947142</v>
       </c>
       <c r="C61">
-        <v>-913.9582243955256</v>
+        <v>-1004.857485040895</v>
       </c>
       <c r="D61">
-        <v>2136.236775604474</v>
+        <v>2111.642514959105</v>
       </c>
       <c r="E61">
-        <v>2025.395</v>
+        <v>2091.7</v>
       </c>
       <c r="F61">
-        <v>3911.995</v>
+        <v>3978.3</v>
       </c>
       <c r="G61">
         <v>861.8</v>
@@ -6295,37 +6295,37 @@
         <v>405.805</v>
       </c>
       <c r="M61">
-        <v>785.528596</v>
+        <v>798.84264</v>
       </c>
       <c r="N61">
-        <v>-379.723596</v>
+        <v>-393.03764</v>
       </c>
       <c r="O61">
-        <v>-37.9723596</v>
+        <v>-39.303764</v>
       </c>
       <c r="P61">
-        <v>-341.7512364</v>
+        <v>-353.733876</v>
       </c>
       <c r="Q61">
-        <v>-336.1812364</v>
+        <v>-348.163876</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09820493463458871</v>
+        <v>0.09951505800045343</v>
       </c>
       <c r="T61">
-        <v>1.050386690944794</v>
+        <v>1.076646358218414</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.05166011804871328</v>
+        <v>0.05079911608123473</v>
       </c>
       <c r="W61">
-        <v>0.1904266482958184</v>
+        <v>0.1905995374908881</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5166011804871328</v>
+        <v>0.5079911608123473</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1541657456947142</v>
+        <v>0.1771660063825568</v>
       </c>
       <c r="C62">
-        <v>-1004.857485040895</v>
+        <v>-1379.274682587872</v>
       </c>
       <c r="D62">
-        <v>2111.642514959105</v>
+        <v>1803.530317412129</v>
       </c>
       <c r="E62">
-        <v>2091.7</v>
+        <v>2158.005</v>
       </c>
       <c r="F62">
-        <v>3978.3</v>
+        <v>4044.605</v>
       </c>
       <c r="G62">
         <v>861.8</v>
@@ -6377,45 +6377,45 @@
         <v>405.805</v>
       </c>
       <c r="M62">
-        <v>798.84264</v>
+        <v>953.7178590000001</v>
       </c>
       <c r="N62">
-        <v>-393.03764</v>
+        <v>-547.912859</v>
       </c>
       <c r="O62">
-        <v>-39.303764</v>
+        <v>-54.79128590000001</v>
       </c>
       <c r="P62">
-        <v>-353.733876</v>
+        <v>-493.1215731</v>
       </c>
       <c r="Q62">
-        <v>-348.163876</v>
+        <v>-487.5515731</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09951505800045343</v>
+        <v>0.1011494458667281</v>
       </c>
       <c r="T62">
-        <v>1.076646358218414</v>
+        <v>1.109405472880938</v>
       </c>
       <c r="U62">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05079911608123473</v>
+        <v>0.04254979564139629</v>
       </c>
       <c r="W62">
-        <v>0.1905995374908881</v>
+        <v>0.2257667581877588</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5079911608123473</v>
+        <v>0.4254979564139629</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1771660063825568</v>
+        <v>0.1790660063825568</v>
       </c>
       <c r="C63">
-        <v>-1379.274682587872</v>
+        <v>-1467.059439321341</v>
       </c>
       <c r="D63">
-        <v>1803.530317412129</v>
+        <v>1782.050560678659</v>
       </c>
       <c r="E63">
-        <v>2158.005</v>
+        <v>2224.31</v>
       </c>
       <c r="F63">
-        <v>4044.605</v>
+        <v>4110.91</v>
       </c>
       <c r="G63">
         <v>861.8</v>
@@ -6459,37 +6459,37 @@
         <v>405.805</v>
       </c>
       <c r="M63">
-        <v>953.7178590000001</v>
+        <v>969.352578</v>
       </c>
       <c r="N63">
-        <v>-547.912859</v>
+        <v>-563.5475779999999</v>
       </c>
       <c r="O63">
-        <v>-54.79128590000001</v>
+        <v>-56.35475779999999</v>
       </c>
       <c r="P63">
-        <v>-493.1215731</v>
+        <v>-507.1928201999999</v>
       </c>
       <c r="Q63">
-        <v>-487.5515731</v>
+        <v>-501.6228201999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1011494458667281</v>
+        <v>0.102606010231642</v>
       </c>
       <c r="T63">
-        <v>1.109405472880938</v>
+        <v>1.138600353746225</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04254979564139629</v>
+        <v>0.04186350861492216</v>
       </c>
       <c r="W63">
-        <v>0.2257667581877588</v>
+        <v>0.2259285846686014</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4254979564139629</v>
+        <v>0.4186350861492216</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1790660063825568</v>
+        <v>0.1809660063825568</v>
       </c>
       <c r="C64">
-        <v>-1467.059439321341</v>
+        <v>-1554.33857698359</v>
       </c>
       <c r="D64">
-        <v>1782.050560678659</v>
+        <v>1761.076423016411</v>
       </c>
       <c r="E64">
-        <v>2224.31</v>
+        <v>2290.615</v>
       </c>
       <c r="F64">
-        <v>4110.91</v>
+        <v>4177.215</v>
       </c>
       <c r="G64">
         <v>861.8</v>
@@ -6541,37 +6541,37 @@
         <v>405.805</v>
       </c>
       <c r="M64">
-        <v>969.352578</v>
+        <v>984.9872970000001</v>
       </c>
       <c r="N64">
-        <v>-563.5475779999999</v>
+        <v>-579.1822970000001</v>
       </c>
       <c r="O64">
-        <v>-56.35475779999999</v>
+        <v>-57.91822970000001</v>
       </c>
       <c r="P64">
-        <v>-507.1928201999999</v>
+        <v>-521.2640673000001</v>
       </c>
       <c r="Q64">
-        <v>-501.6228201999999</v>
+        <v>-515.6940673</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.102606010231642</v>
+        <v>0.1041413078054702</v>
       </c>
       <c r="T64">
-        <v>1.138600353746225</v>
+        <v>1.169373336279907</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04186350861492216</v>
+        <v>0.04119900847817735</v>
       </c>
       <c r="W64">
-        <v>0.2259285846686014</v>
+        <v>0.2260852738008458</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4186350861492216</v>
+        <v>0.4119900847817736</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1809660063825568</v>
+        <v>0.1828660063825568</v>
       </c>
       <c r="C65">
-        <v>-1554.33857698359</v>
+        <v>-1641.129740797138</v>
       </c>
       <c r="D65">
-        <v>1761.076423016411</v>
+        <v>1740.590259202862</v>
       </c>
       <c r="E65">
-        <v>2290.615</v>
+        <v>2356.920000000001</v>
       </c>
       <c r="F65">
-        <v>4177.215</v>
+        <v>4243.52</v>
       </c>
       <c r="G65">
         <v>861.8</v>
@@ -6623,37 +6623,37 @@
         <v>405.805</v>
       </c>
       <c r="M65">
-        <v>984.9872970000001</v>
+        <v>1000.622016</v>
       </c>
       <c r="N65">
-        <v>-579.1822970000001</v>
+        <v>-594.8170160000002</v>
       </c>
       <c r="O65">
-        <v>-57.91822970000001</v>
+        <v>-59.48170160000002</v>
       </c>
       <c r="P65">
-        <v>-521.2640673000001</v>
+        <v>-535.3353144000001</v>
       </c>
       <c r="Q65">
-        <v>-515.6940673</v>
+        <v>-529.7653144000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1041413078054702</v>
+        <v>0.1057618996889554</v>
       </c>
       <c r="T65">
-        <v>1.169373336279907</v>
+        <v>1.201855928954349</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04119900847817735</v>
+        <v>0.04055527397070583</v>
       </c>
       <c r="W65">
-        <v>0.2260852738008458</v>
+        <v>0.2262370663977076</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4119900847817736</v>
+        <v>0.4055527397070583</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1828660063825568</v>
+        <v>0.1847660063825568</v>
       </c>
       <c r="C66">
-        <v>-1641.129740797138</v>
+        <v>-1727.449764375819</v>
       </c>
       <c r="D66">
-        <v>1740.590259202862</v>
+        <v>1720.575235624181</v>
       </c>
       <c r="E66">
-        <v>2356.920000000001</v>
+        <v>2423.225</v>
       </c>
       <c r="F66">
-        <v>4243.52</v>
+        <v>4309.825</v>
       </c>
       <c r="G66">
         <v>861.8</v>
@@ -6705,37 +6705,37 @@
         <v>405.805</v>
       </c>
       <c r="M66">
-        <v>1000.622016</v>
+        <v>1016.256735</v>
       </c>
       <c r="N66">
-        <v>-594.8170160000002</v>
+        <v>-610.4517350000001</v>
       </c>
       <c r="O66">
-        <v>-59.48170160000002</v>
+        <v>-61.04517350000001</v>
       </c>
       <c r="P66">
-        <v>-535.3353144000001</v>
+        <v>-549.4065615000001</v>
       </c>
       <c r="Q66">
-        <v>-529.7653144000001</v>
+        <v>-543.8365615</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1057618996889554</v>
+        <v>0.1074750968229256</v>
       </c>
       <c r="T66">
-        <v>1.201855928954349</v>
+        <v>1.236194669781616</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04055527397070583</v>
+        <v>0.03993134667884882</v>
       </c>
       <c r="W66">
-        <v>0.2262370663977076</v>
+        <v>0.2263841884531275</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4055527397070583</v>
+        <v>0.3993134667884882</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1847660063825568</v>
+        <v>0.1866660063825568</v>
       </c>
       <c r="C67">
-        <v>-1727.449764375819</v>
+        <v>-1813.314715857678</v>
       </c>
       <c r="D67">
-        <v>1720.575235624181</v>
+        <v>1701.015284142322</v>
       </c>
       <c r="E67">
-        <v>2423.225</v>
+        <v>2489.53</v>
       </c>
       <c r="F67">
-        <v>4309.825</v>
+        <v>4376.13</v>
       </c>
       <c r="G67">
         <v>861.8</v>
@@ -6787,37 +6787,37 @@
         <v>405.805</v>
       </c>
       <c r="M67">
-        <v>1016.256735</v>
+        <v>1031.891454</v>
       </c>
       <c r="N67">
-        <v>-610.4517350000001</v>
+        <v>-626.086454</v>
       </c>
       <c r="O67">
-        <v>-61.04517350000001</v>
+        <v>-62.6086454</v>
       </c>
       <c r="P67">
-        <v>-549.4065615000001</v>
+        <v>-563.4778086</v>
       </c>
       <c r="Q67">
-        <v>-543.8365615</v>
+        <v>-557.9078086</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1074750968229256</v>
+        <v>0.109289070258894</v>
       </c>
       <c r="T67">
-        <v>1.236194669781616</v>
+        <v>1.272553336539899</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03993134667884882</v>
+        <v>0.03932632627462385</v>
       </c>
       <c r="W67">
-        <v>0.2263841884531275</v>
+        <v>0.2265268522644437</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3993134667884882</v>
+        <v>0.3932632627462385</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1866660063825568</v>
+        <v>0.1885660063825568</v>
       </c>
       <c r="C68">
-        <v>-1813.314715857678</v>
+        <v>-1898.739940926547</v>
       </c>
       <c r="D68">
-        <v>1701.015284142322</v>
+        <v>1681.895059073453</v>
       </c>
       <c r="E68">
-        <v>2489.53</v>
+        <v>2555.835</v>
       </c>
       <c r="F68">
-        <v>4376.13</v>
+        <v>4442.435</v>
       </c>
       <c r="G68">
         <v>861.8</v>
@@ -6869,37 +6869,37 @@
         <v>405.805</v>
       </c>
       <c r="M68">
-        <v>1031.891454</v>
+        <v>1047.526173</v>
       </c>
       <c r="N68">
-        <v>-626.086454</v>
+        <v>-641.7211730000001</v>
       </c>
       <c r="O68">
-        <v>-62.6086454</v>
+        <v>-64.17211730000001</v>
       </c>
       <c r="P68">
-        <v>-563.4778086</v>
+        <v>-577.5490557000002</v>
       </c>
       <c r="Q68">
-        <v>-557.9078086</v>
+        <v>-571.9790557000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.109289070258894</v>
+        <v>0.1112129814788605</v>
       </c>
       <c r="T68">
-        <v>1.272553336539899</v>
+        <v>1.31111555885929</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03932632627462385</v>
+        <v>0.03873936618097273</v>
       </c>
       <c r="W68">
-        <v>0.2265268522644437</v>
+        <v>0.2266652574545266</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3932632627462385</v>
+        <v>0.3873936618097273</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1885660063825568</v>
+        <v>0.1904660063825568</v>
       </c>
       <c r="C69">
-        <v>-1898.739940926547</v>
+        <v>-1983.740102964362</v>
       </c>
       <c r="D69">
-        <v>1681.895059073453</v>
+        <v>1663.199897035639</v>
       </c>
       <c r="E69">
-        <v>2555.835</v>
+        <v>2622.140000000001</v>
       </c>
       <c r="F69">
-        <v>4442.435</v>
+        <v>4508.740000000001</v>
       </c>
       <c r="G69">
         <v>861.8</v>
@@ -6951,37 +6951,37 @@
         <v>405.805</v>
       </c>
       <c r="M69">
-        <v>1047.526173</v>
+        <v>1063.160892</v>
       </c>
       <c r="N69">
-        <v>-641.7211730000001</v>
+        <v>-657.355892</v>
       </c>
       <c r="O69">
-        <v>-64.17211730000001</v>
+        <v>-65.73558920000001</v>
       </c>
       <c r="P69">
-        <v>-577.5490557000002</v>
+        <v>-591.6203028</v>
       </c>
       <c r="Q69">
-        <v>-571.9790557000001</v>
+        <v>-586.0503027999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1112129814788605</v>
+        <v>0.1132571371500749</v>
       </c>
       <c r="T69">
-        <v>1.31111555885929</v>
+        <v>1.352087920073643</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03873936618097273</v>
+        <v>0.03816966961948785</v>
       </c>
       <c r="W69">
-        <v>0.2266652574545266</v>
+        <v>0.2267995919037248</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3873936618097273</v>
+        <v>0.3816966961948784</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1904660063825568</v>
+        <v>0.1923660063825568</v>
       </c>
       <c r="C70">
-        <v>-1983.740102964362</v>
+        <v>-2068.329220555041</v>
       </c>
       <c r="D70">
-        <v>1663.199897035639</v>
+        <v>1644.91577944496</v>
       </c>
       <c r="E70">
-        <v>2622.140000000001</v>
+        <v>2688.445</v>
       </c>
       <c r="F70">
-        <v>4508.740000000001</v>
+        <v>4575.045</v>
       </c>
       <c r="G70">
         <v>861.8</v>
@@ -7033,37 +7033,37 @@
         <v>405.805</v>
       </c>
       <c r="M70">
-        <v>1063.160892</v>
+        <v>1078.795611</v>
       </c>
       <c r="N70">
-        <v>-657.355892</v>
+        <v>-672.9906109999999</v>
       </c>
       <c r="O70">
-        <v>-65.73558920000001</v>
+        <v>-67.2990611</v>
       </c>
       <c r="P70">
-        <v>-591.6203028</v>
+        <v>-605.6915498999999</v>
       </c>
       <c r="Q70">
-        <v>-586.0503027999999</v>
+        <v>-600.1215498999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1132571371500749</v>
+        <v>0.1154331738323353</v>
       </c>
       <c r="T70">
-        <v>1.352087920073643</v>
+        <v>1.395703659430857</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03816966961948785</v>
+        <v>0.03761648600181411</v>
       </c>
       <c r="W70">
-        <v>0.2267995919037248</v>
+        <v>0.2269300326007722</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3816966961948784</v>
+        <v>0.3761648600181412</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1923660063825568</v>
+        <v>0.1942660063825568</v>
       </c>
       <c r="C71">
-        <v>-2068.329220555041</v>
+        <v>-2152.520702541502</v>
       </c>
       <c r="D71">
-        <v>1644.91577944496</v>
+        <v>1627.029297458498</v>
       </c>
       <c r="E71">
-        <v>2688.445</v>
+        <v>2754.75</v>
       </c>
       <c r="F71">
-        <v>4575.045</v>
+        <v>4641.35</v>
       </c>
       <c r="G71">
         <v>861.8</v>
@@ -7115,37 +7115,37 @@
         <v>405.805</v>
       </c>
       <c r="M71">
-        <v>1078.795611</v>
+        <v>1094.43033</v>
       </c>
       <c r="N71">
-        <v>-672.9906109999999</v>
+        <v>-688.6253300000001</v>
       </c>
       <c r="O71">
-        <v>-67.2990611</v>
+        <v>-68.86253300000001</v>
       </c>
       <c r="P71">
-        <v>-605.6915498999999</v>
+        <v>-619.7627970000001</v>
       </c>
       <c r="Q71">
-        <v>-600.1215498999999</v>
+        <v>-614.192797</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1154331738323353</v>
+        <v>0.1177542796267465</v>
       </c>
       <c r="T71">
-        <v>1.395703659430857</v>
+        <v>1.442227114745219</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03761648600181411</v>
+        <v>0.03707910763035962</v>
       </c>
       <c r="W71">
-        <v>0.2269300326007722</v>
+        <v>0.2270567464207612</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3761648600181412</v>
+        <v>0.3707910763035962</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1942660063825568</v>
+        <v>0.1961660063825568</v>
       </c>
       <c r="C72">
-        <v>-2152.520702541502</v>
+        <v>-2236.327380820064</v>
       </c>
       <c r="D72">
-        <v>1627.029297458498</v>
+        <v>1609.527619179937</v>
       </c>
       <c r="E72">
-        <v>2754.75</v>
+        <v>2821.055000000001</v>
       </c>
       <c r="F72">
-        <v>4641.35</v>
+        <v>4707.655000000001</v>
       </c>
       <c r="G72">
         <v>861.8</v>
@@ -7197,37 +7197,37 @@
         <v>405.805</v>
       </c>
       <c r="M72">
-        <v>1094.43033</v>
+        <v>1110.065049</v>
       </c>
       <c r="N72">
-        <v>-688.6253300000001</v>
+        <v>-704.2600490000002</v>
       </c>
       <c r="O72">
-        <v>-68.86253300000001</v>
+        <v>-70.42600490000002</v>
       </c>
       <c r="P72">
-        <v>-619.7627970000001</v>
+        <v>-633.8340441000001</v>
       </c>
       <c r="Q72">
-        <v>-614.192797</v>
+        <v>-628.2640441000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1177542796267465</v>
+        <v>0.1202354616828412</v>
       </c>
       <c r="T72">
-        <v>1.442227114745219</v>
+        <v>1.491959084219193</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03707910763035962</v>
+        <v>0.03655686667781934</v>
       </c>
       <c r="W72">
-        <v>0.2270567464207612</v>
+        <v>0.2271798908373702</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3707910763035962</v>
+        <v>0.3655686667781934</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1961660063825568</v>
+        <v>0.1980660063825568</v>
       </c>
       <c r="C73">
-        <v>-2236.327380820063</v>
+        <v>-2319.761541040787</v>
       </c>
       <c r="D73">
-        <v>1609.527619179937</v>
+        <v>1592.398458959213</v>
       </c>
       <c r="E73">
-        <v>2821.055</v>
+        <v>2887.36</v>
       </c>
       <c r="F73">
-        <v>4707.655</v>
+        <v>4773.96</v>
       </c>
       <c r="G73">
         <v>861.8</v>
@@ -7279,37 +7279,37 @@
         <v>405.805</v>
       </c>
       <c r="M73">
-        <v>1110.065049</v>
+        <v>1125.699768</v>
       </c>
       <c r="N73">
-        <v>-704.260049</v>
+        <v>-719.8947679999999</v>
       </c>
       <c r="O73">
-        <v>-70.4260049</v>
+        <v>-71.98947679999999</v>
       </c>
       <c r="P73">
-        <v>-633.8340441</v>
+        <v>-647.9052911999999</v>
       </c>
       <c r="Q73">
-        <v>-628.2640441</v>
+        <v>-642.3352911999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1202354616828412</v>
+        <v>0.122893871028657</v>
       </c>
       <c r="T73">
-        <v>1.491959084219192</v>
+        <v>1.54524333722702</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03655686667781934</v>
+        <v>0.03604913241840519</v>
       </c>
       <c r="W73">
-        <v>0.2271798908373702</v>
+        <v>0.22729961457574</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3655686667781936</v>
+        <v>0.3604913241840519</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1980660063825568</v>
+        <v>0.1999660063825568</v>
       </c>
       <c r="C74">
-        <v>-2319.761541040787</v>
+        <v>-2402.834951368132</v>
       </c>
       <c r="D74">
-        <v>1592.398458959213</v>
+        <v>1575.630048631868</v>
       </c>
       <c r="E74">
-        <v>2887.36</v>
+        <v>2953.665</v>
       </c>
       <c r="F74">
-        <v>4773.96</v>
+        <v>4840.265</v>
       </c>
       <c r="G74">
         <v>861.8</v>
@@ -7361,37 +7361,37 @@
         <v>405.805</v>
       </c>
       <c r="M74">
-        <v>1125.699768</v>
+        <v>1141.334487</v>
       </c>
       <c r="N74">
-        <v>-719.8947679999999</v>
+        <v>-735.529487</v>
       </c>
       <c r="O74">
-        <v>-71.98947679999999</v>
+        <v>-73.5529487</v>
       </c>
       <c r="P74">
-        <v>-647.9052911999999</v>
+        <v>-661.9765383</v>
       </c>
       <c r="Q74">
-        <v>-642.3352911999998</v>
+        <v>-656.4065383</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.122893871028657</v>
+        <v>0.1257491995852739</v>
       </c>
       <c r="T74">
-        <v>1.54524333722702</v>
+        <v>1.602474571939132</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03604913241840519</v>
+        <v>0.03555530868664621</v>
       </c>
       <c r="W74">
-        <v>0.22729961457574</v>
+        <v>0.2274160582116888</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3604913241840519</v>
+        <v>0.3555530868664621</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1999660063825568</v>
+        <v>0.2018660063825568</v>
       </c>
       <c r="C75">
-        <v>-2402.834951368132</v>
+        <v>-2485.558889443378</v>
       </c>
       <c r="D75">
-        <v>1575.630048631868</v>
+        <v>1559.211110556622</v>
       </c>
       <c r="E75">
-        <v>2953.665</v>
+        <v>3019.97</v>
       </c>
       <c r="F75">
-        <v>4840.265</v>
+        <v>4906.57</v>
       </c>
       <c r="G75">
         <v>861.8</v>
@@ -7443,37 +7443,37 @@
         <v>405.805</v>
       </c>
       <c r="M75">
-        <v>1141.334487</v>
+        <v>1156.969206</v>
       </c>
       <c r="N75">
-        <v>-735.529487</v>
+        <v>-751.1642059999999</v>
       </c>
       <c r="O75">
-        <v>-73.5529487</v>
+        <v>-75.1164206</v>
       </c>
       <c r="P75">
-        <v>-661.9765383</v>
+        <v>-676.0477854</v>
       </c>
       <c r="Q75">
-        <v>-656.4065383</v>
+        <v>-670.4777853999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1257491995852739</v>
+        <v>0.1288241688000921</v>
       </c>
       <c r="T75">
-        <v>1.602474571939132</v>
+        <v>1.664108209321406</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03555530868664621</v>
+        <v>0.03507483154223208</v>
       </c>
       <c r="W75">
-        <v>0.2274160582116888</v>
+        <v>0.2275293547223417</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3555530868664621</v>
+        <v>0.3507483154223208</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2018660063825568</v>
+        <v>0.2037660063825568</v>
       </c>
       <c r="C76">
-        <v>-2485.558889443378</v>
+        <v>-2567.94416767867</v>
       </c>
       <c r="D76">
-        <v>1559.211110556622</v>
+        <v>1543.13083232133</v>
       </c>
       <c r="E76">
-        <v>3019.97</v>
+        <v>3086.275</v>
       </c>
       <c r="F76">
-        <v>4906.57</v>
+        <v>4972.875</v>
       </c>
       <c r="G76">
         <v>861.8</v>
@@ -7525,37 +7525,37 @@
         <v>405.805</v>
       </c>
       <c r="M76">
-        <v>1156.969206</v>
+        <v>1172.603925</v>
       </c>
       <c r="N76">
-        <v>-751.1642059999999</v>
+        <v>-766.7989250000001</v>
       </c>
       <c r="O76">
-        <v>-75.1164206</v>
+        <v>-76.67989250000001</v>
       </c>
       <c r="P76">
-        <v>-676.0477854</v>
+        <v>-690.1190325</v>
       </c>
       <c r="Q76">
-        <v>-670.4777853999999</v>
+        <v>-684.5490325</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1288241688000921</v>
+        <v>0.1321451355520958</v>
       </c>
       <c r="T76">
-        <v>1.664108209321406</v>
+        <v>1.730672537694262</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03507483154223208</v>
+        <v>0.03460716712166898</v>
       </c>
       <c r="W76">
-        <v>0.2275293547223417</v>
+        <v>0.2276396299927105</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3507483154223208</v>
+        <v>0.3460716712166898</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2037660063825568</v>
+        <v>0.2056660063825568</v>
       </c>
       <c r="C77">
-        <v>-2567.94416767867</v>
+        <v>-2650.001157001874</v>
       </c>
       <c r="D77">
-        <v>1543.13083232133</v>
+        <v>1527.378842998126</v>
       </c>
       <c r="E77">
-        <v>3086.275</v>
+        <v>3152.58</v>
       </c>
       <c r="F77">
-        <v>4972.875</v>
+        <v>5039.18</v>
       </c>
       <c r="G77">
         <v>861.8</v>
@@ -7607,37 +7607,37 @@
         <v>405.805</v>
       </c>
       <c r="M77">
-        <v>1172.603925</v>
+        <v>1188.238644</v>
       </c>
       <c r="N77">
-        <v>-766.7989250000001</v>
+        <v>-782.433644</v>
       </c>
       <c r="O77">
-        <v>-76.67989250000001</v>
+        <v>-78.2433644</v>
       </c>
       <c r="P77">
-        <v>-690.1190325</v>
+        <v>-704.1902795999999</v>
       </c>
       <c r="Q77">
-        <v>-684.5490325</v>
+        <v>-698.6202795999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1321451355520958</v>
+        <v>0.1357428495334332</v>
       </c>
       <c r="T77">
-        <v>1.730672537694262</v>
+        <v>1.802783893431524</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03460716712166898</v>
+        <v>0.03415180965954176</v>
       </c>
       <c r="W77">
-        <v>0.2276396299927105</v>
+        <v>0.2277470032822801</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3460716712166898</v>
+        <v>0.3415180965954177</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2056660063825568</v>
+        <v>0.2075660063825568</v>
       </c>
       <c r="C78">
-        <v>-2650.001157001874</v>
+        <v>-2731.73980916183</v>
       </c>
       <c r="D78">
-        <v>1527.378842998126</v>
+        <v>1511.94519083817</v>
       </c>
       <c r="E78">
-        <v>3152.58</v>
+        <v>3218.885</v>
       </c>
       <c r="F78">
-        <v>5039.18</v>
+        <v>5105.485</v>
       </c>
       <c r="G78">
         <v>861.8</v>
@@ -7689,37 +7689,37 @@
         <v>405.805</v>
       </c>
       <c r="M78">
-        <v>1188.238644</v>
+        <v>1203.873363</v>
       </c>
       <c r="N78">
-        <v>-782.433644</v>
+        <v>-798.0683629999999</v>
       </c>
       <c r="O78">
-        <v>-78.2433644</v>
+        <v>-79.80683629999999</v>
       </c>
       <c r="P78">
-        <v>-704.1902795999999</v>
+        <v>-718.2615266999999</v>
       </c>
       <c r="Q78">
-        <v>-698.6202795999999</v>
+        <v>-712.6915266999998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1357428495334332</v>
+        <v>0.1396534082087998</v>
       </c>
       <c r="T78">
-        <v>1.802783893431524</v>
+        <v>1.88116580184159</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03415180965954176</v>
+        <v>0.0337082796639633</v>
       </c>
       <c r="W78">
-        <v>0.2277470032822801</v>
+        <v>0.2278515876552375</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3415180965954177</v>
+        <v>0.337082796639633</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2075660063825568</v>
+        <v>0.2094660063825568</v>
       </c>
       <c r="C79">
-        <v>-2731.73980916183</v>
+        <v>-2813.169677694817</v>
       </c>
       <c r="D79">
-        <v>1511.94519083817</v>
+        <v>1496.820322305183</v>
       </c>
       <c r="E79">
-        <v>3218.885</v>
+        <v>3285.19</v>
       </c>
       <c r="F79">
-        <v>5105.485</v>
+        <v>5171.79</v>
       </c>
       <c r="G79">
         <v>861.8</v>
@@ -7771,37 +7771,37 @@
         <v>405.805</v>
       </c>
       <c r="M79">
-        <v>1203.873363</v>
+        <v>1219.508082</v>
       </c>
       <c r="N79">
-        <v>-798.0683629999999</v>
+        <v>-813.703082</v>
       </c>
       <c r="O79">
-        <v>-79.80683629999999</v>
+        <v>-81.37030820000001</v>
       </c>
       <c r="P79">
-        <v>-718.2615266999999</v>
+        <v>-732.3327738</v>
       </c>
       <c r="Q79">
-        <v>-712.6915266999998</v>
+        <v>-726.7627738</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1396534082087998</v>
+        <v>0.1439194722182907</v>
       </c>
       <c r="T79">
-        <v>1.88116580184159</v>
+        <v>1.966673338288935</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0337082796639633</v>
+        <v>0.03327612223237402</v>
       </c>
       <c r="W79">
-        <v>0.2278515876552375</v>
+        <v>0.2279534903776062</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.337082796639633</v>
+        <v>0.3327612223237403</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2094660063825568</v>
+        <v>0.2113660063825568</v>
       </c>
       <c r="C80">
-        <v>-2813.169677694817</v>
+        <v>-2894.299937645033</v>
       </c>
       <c r="D80">
-        <v>1496.820322305183</v>
+        <v>1481.995062354967</v>
       </c>
       <c r="E80">
-        <v>3285.19</v>
+        <v>3351.495</v>
       </c>
       <c r="F80">
-        <v>5171.79</v>
+        <v>5238.095</v>
       </c>
       <c r="G80">
         <v>861.8</v>
@@ -7853,37 +7853,37 @@
         <v>405.805</v>
       </c>
       <c r="M80">
-        <v>1219.508082</v>
+        <v>1235.142801</v>
       </c>
       <c r="N80">
-        <v>-813.703082</v>
+        <v>-829.3378010000001</v>
       </c>
       <c r="O80">
-        <v>-81.37030820000001</v>
+        <v>-82.93378010000002</v>
       </c>
       <c r="P80">
-        <v>-732.3327738</v>
+        <v>-746.4040209000001</v>
       </c>
       <c r="Q80">
-        <v>-726.7627738</v>
+        <v>-740.8340209</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1439194722182907</v>
+        <v>0.1485918280382093</v>
       </c>
       <c r="T80">
-        <v>1.966673338288935</v>
+        <v>2.060324449636028</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03327612223237402</v>
+        <v>0.03285490549525536</v>
       </c>
       <c r="W80">
-        <v>0.2279534903776062</v>
+        <v>0.2280528132842188</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3327612223237403</v>
+        <v>0.3285490549525536</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2113660063825568</v>
+        <v>0.2132660063825568</v>
       </c>
       <c r="C81">
-        <v>-2894.299937645033</v>
+        <v>-2975.139404124648</v>
       </c>
       <c r="D81">
-        <v>1481.995062354967</v>
+        <v>1467.460595875353</v>
       </c>
       <c r="E81">
-        <v>3351.495</v>
+        <v>3417.800000000001</v>
       </c>
       <c r="F81">
-        <v>5238.095</v>
+        <v>5304.400000000001</v>
       </c>
       <c r="G81">
         <v>861.8</v>
@@ -7935,37 +7935,37 @@
         <v>405.805</v>
       </c>
       <c r="M81">
-        <v>1235.142801</v>
+        <v>1250.77752</v>
       </c>
       <c r="N81">
-        <v>-829.3378010000001</v>
+        <v>-844.97252</v>
       </c>
       <c r="O81">
-        <v>-82.93378010000002</v>
+        <v>-84.497252</v>
       </c>
       <c r="P81">
-        <v>-746.4040209000001</v>
+        <v>-760.475268</v>
       </c>
       <c r="Q81">
-        <v>-740.8340209</v>
+        <v>-754.905268</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1485918280382093</v>
+        <v>0.1537314194401198</v>
       </c>
       <c r="T81">
-        <v>2.060324449636028</v>
+        <v>2.163340672117829</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03285490549525536</v>
+        <v>0.03244421917656467</v>
       </c>
       <c r="W81">
-        <v>0.2280528132842188</v>
+        <v>0.228149653118166</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3285490549525536</v>
+        <v>0.3244421917656467</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2132660063825568</v>
+        <v>0.2151660063825568</v>
       </c>
       <c r="C82">
-        <v>-2975.139404124648</v>
+        <v>-3055.696549792307</v>
       </c>
       <c r="D82">
-        <v>1467.460595875353</v>
+        <v>1453.208450207692</v>
       </c>
       <c r="E82">
-        <v>3417.800000000001</v>
+        <v>3484.105</v>
       </c>
       <c r="F82">
-        <v>5304.400000000001</v>
+        <v>5370.705</v>
       </c>
       <c r="G82">
         <v>861.8</v>
@@ -8017,37 +8017,37 @@
         <v>405.805</v>
       </c>
       <c r="M82">
-        <v>1250.77752</v>
+        <v>1266.412239</v>
       </c>
       <c r="N82">
-        <v>-844.97252</v>
+        <v>-860.6072389999999</v>
       </c>
       <c r="O82">
-        <v>-84.497252</v>
+        <v>-86.0607239</v>
       </c>
       <c r="P82">
-        <v>-760.475268</v>
+        <v>-774.5465151</v>
       </c>
       <c r="Q82">
-        <v>-754.905268</v>
+        <v>-768.9765150999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1537314194401198</v>
+        <v>0.159412020463284</v>
       </c>
       <c r="T82">
-        <v>2.163340672117829</v>
+        <v>2.277200707492451</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03244421917656467</v>
+        <v>0.03204367326080462</v>
       </c>
       <c r="W82">
-        <v>0.228149653118166</v>
+        <v>0.2282441018451023</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3244421917656467</v>
+        <v>0.3204367326080462</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2151660063825568</v>
+        <v>0.2170660063825568</v>
       </c>
       <c r="C83">
-        <v>-3055.696549792307</v>
+        <v>-3135.979521322922</v>
       </c>
       <c r="D83">
-        <v>1453.208450207692</v>
+        <v>1439.230478677079</v>
       </c>
       <c r="E83">
-        <v>3484.105</v>
+        <v>3550.41</v>
       </c>
       <c r="F83">
-        <v>5370.705</v>
+        <v>5437.01</v>
       </c>
       <c r="G83">
         <v>861.8</v>
@@ -8099,37 +8099,37 @@
         <v>405.805</v>
       </c>
       <c r="M83">
-        <v>1266.412239</v>
+        <v>1282.046958</v>
       </c>
       <c r="N83">
-        <v>-860.6072389999999</v>
+        <v>-876.2419580000001</v>
       </c>
       <c r="O83">
-        <v>-86.0607239</v>
+        <v>-87.62419580000001</v>
       </c>
       <c r="P83">
-        <v>-774.5465151</v>
+        <v>-788.6177622</v>
       </c>
       <c r="Q83">
-        <v>-768.9765150999999</v>
+        <v>-783.0477622</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.159412020463284</v>
+        <v>0.1657237993779109</v>
       </c>
       <c r="T83">
-        <v>2.277200707492451</v>
+        <v>2.403711857908699</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03204367326080462</v>
+        <v>0.03165289675762407</v>
       </c>
       <c r="W83">
-        <v>0.2282441018451023</v>
+        <v>0.2283362469445523</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3204367326080462</v>
+        <v>0.3165289675762407</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2170660063825568</v>
+        <v>0.2189660063825568</v>
       </c>
       <c r="C84">
-        <v>-3135.979521322922</v>
+        <v>-3215.996154935986</v>
       </c>
       <c r="D84">
-        <v>1439.230478677079</v>
+        <v>1425.518845064014</v>
       </c>
       <c r="E84">
-        <v>3550.41</v>
+        <v>3616.715000000001</v>
       </c>
       <c r="F84">
-        <v>5437.01</v>
+        <v>5503.315000000001</v>
       </c>
       <c r="G84">
         <v>861.8</v>
@@ -8181,37 +8181,37 @@
         <v>405.805</v>
       </c>
       <c r="M84">
-        <v>1282.046958</v>
+        <v>1297.681677</v>
       </c>
       <c r="N84">
-        <v>-876.2419580000001</v>
+        <v>-891.8766770000002</v>
       </c>
       <c r="O84">
-        <v>-87.62419580000001</v>
+        <v>-89.18766770000002</v>
       </c>
       <c r="P84">
-        <v>-788.6177622</v>
+        <v>-802.6890093000002</v>
       </c>
       <c r="Q84">
-        <v>-783.0477622</v>
+        <v>-797.1190093000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1657237993779109</v>
+        <v>0.172778140517788</v>
       </c>
       <c r="T84">
-        <v>2.403711857908699</v>
+        <v>2.545106673079799</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03165289675762407</v>
+        <v>0.03127153655572498</v>
       </c>
       <c r="W84">
-        <v>0.2283362469445523</v>
+        <v>0.2284261716801601</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3165289675762407</v>
+        <v>0.3127153655572498</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2189660063825568</v>
+        <v>0.2208660063825568</v>
       </c>
       <c r="C85">
-        <v>-3215.996154935986</v>
+        <v>-3295.753991044665</v>
       </c>
       <c r="D85">
-        <v>1425.518845064014</v>
+        <v>1412.066008955336</v>
       </c>
       <c r="E85">
-        <v>3616.715000000001</v>
+        <v>3683.020000000001</v>
       </c>
       <c r="F85">
-        <v>5503.315000000001</v>
+        <v>5569.620000000001</v>
       </c>
       <c r="G85">
         <v>861.8</v>
@@ -8263,37 +8263,37 @@
         <v>405.805</v>
       </c>
       <c r="M85">
-        <v>1297.681677</v>
+        <v>1313.316396</v>
       </c>
       <c r="N85">
-        <v>-891.8766770000002</v>
+        <v>-907.5113960000001</v>
       </c>
       <c r="O85">
-        <v>-89.18766770000002</v>
+        <v>-90.75113960000002</v>
       </c>
       <c r="P85">
-        <v>-802.6890093000002</v>
+        <v>-816.7602564000001</v>
       </c>
       <c r="Q85">
-        <v>-797.1190093000001</v>
+        <v>-811.1902564000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.172778140517788</v>
+        <v>0.1807142743001498</v>
       </c>
       <c r="T85">
-        <v>2.545106673079799</v>
+        <v>2.704175840147287</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03127153655572498</v>
+        <v>0.03089925635863302</v>
       </c>
       <c r="W85">
-        <v>0.2284261716801601</v>
+        <v>0.2285139553506343</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3127153655572498</v>
+        <v>0.3089925635863302</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2208660063825568</v>
+        <v>0.2227660063825568</v>
       </c>
       <c r="C86">
-        <v>-3295.753991044664</v>
+        <v>-3375.260288083137</v>
       </c>
       <c r="D86">
-        <v>1412.066008955336</v>
+        <v>1398.864711916863</v>
       </c>
       <c r="E86">
-        <v>3683.02</v>
+        <v>3749.325</v>
       </c>
       <c r="F86">
-        <v>5569.62</v>
+        <v>5635.925</v>
       </c>
       <c r="G86">
         <v>861.8</v>
@@ -8345,37 +8345,37 @@
         <v>405.805</v>
       </c>
       <c r="M86">
-        <v>1313.316396</v>
+        <v>1328.951115</v>
       </c>
       <c r="N86">
-        <v>-907.5113959999999</v>
+        <v>-923.146115</v>
       </c>
       <c r="O86">
-        <v>-90.75113959999999</v>
+        <v>-92.31461150000001</v>
       </c>
       <c r="P86">
-        <v>-816.7602563999999</v>
+        <v>-830.8315035000001</v>
       </c>
       <c r="Q86">
-        <v>-811.1902563999998</v>
+        <v>-825.2615035</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1807142743001497</v>
+        <v>0.189708559253493</v>
       </c>
       <c r="T86">
-        <v>2.704175840147285</v>
+        <v>2.884454229490438</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03089925635863302</v>
+        <v>0.03053573569559028</v>
       </c>
       <c r="W86">
-        <v>0.2285139553506343</v>
+        <v>0.2285996735229798</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3089925635863302</v>
+        <v>0.3053573569559028</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2227660063825568</v>
+        <v>0.2246660063825568</v>
       </c>
       <c r="C87">
-        <v>-3375.260288083137</v>
+        <v>-3454.522035565517</v>
       </c>
       <c r="D87">
-        <v>1398.864711916863</v>
+        <v>1385.907964434483</v>
       </c>
       <c r="E87">
-        <v>3749.325</v>
+        <v>3815.63</v>
       </c>
       <c r="F87">
-        <v>5635.925</v>
+        <v>5702.23</v>
       </c>
       <c r="G87">
         <v>861.8</v>
@@ -8427,37 +8427,37 @@
         <v>405.805</v>
       </c>
       <c r="M87">
-        <v>1328.951115</v>
+        <v>1344.585834</v>
       </c>
       <c r="N87">
-        <v>-923.146115</v>
+        <v>-938.7808339999999</v>
       </c>
       <c r="O87">
-        <v>-92.31461150000001</v>
+        <v>-93.87808339999999</v>
       </c>
       <c r="P87">
-        <v>-830.8315035000001</v>
+        <v>-844.9027505999999</v>
       </c>
       <c r="Q87">
-        <v>-825.2615035</v>
+        <v>-839.3327505999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.189708559253493</v>
+        <v>0.199987742057314</v>
       </c>
       <c r="T87">
-        <v>2.884454229490438</v>
+        <v>3.09048667445404</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03053573569559028</v>
+        <v>0.03018066900145551</v>
       </c>
       <c r="W87">
-        <v>0.2285996735229798</v>
+        <v>0.2286833982494568</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3053573569559028</v>
+        <v>0.3018066900145551</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2246660063825568</v>
+        <v>0.2265660063825568</v>
       </c>
       <c r="C88">
-        <v>-3454.522035565517</v>
+        <v>-3533.545966425682</v>
       </c>
       <c r="D88">
-        <v>1385.907964434483</v>
+        <v>1373.189033574318</v>
       </c>
       <c r="E88">
-        <v>3815.63</v>
+        <v>3881.935</v>
       </c>
       <c r="F88">
-        <v>5702.23</v>
+        <v>5768.535</v>
       </c>
       <c r="G88">
         <v>861.8</v>
@@ -8509,37 +8509,37 @@
         <v>405.805</v>
       </c>
       <c r="M88">
-        <v>1344.585834</v>
+        <v>1360.220553</v>
       </c>
       <c r="N88">
-        <v>-938.7808339999999</v>
+        <v>-954.415553</v>
       </c>
       <c r="O88">
-        <v>-93.87808339999999</v>
+        <v>-95.4415553</v>
       </c>
       <c r="P88">
-        <v>-844.9027505999999</v>
+        <v>-858.9739977</v>
       </c>
       <c r="Q88">
-        <v>-839.3327505999998</v>
+        <v>-853.4039977</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.199987742057314</v>
+        <v>0.2118483376001843</v>
       </c>
       <c r="T88">
-        <v>3.09048667445404</v>
+        <v>3.328216418642813</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03018066900145551</v>
+        <v>0.02983376476005947</v>
       </c>
       <c r="W88">
-        <v>0.2286833982494568</v>
+        <v>0.228765198269578</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3018066900145551</v>
+        <v>0.2983376476005947</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2265660063825568</v>
+        <v>0.2284660063825568</v>
       </c>
       <c r="C89">
-        <v>-3533.545966425682</v>
+        <v>-3612.338568683816</v>
       </c>
       <c r="D89">
-        <v>1373.189033574318</v>
+        <v>1360.701431316184</v>
       </c>
       <c r="E89">
-        <v>3881.935</v>
+        <v>3948.24</v>
       </c>
       <c r="F89">
-        <v>5768.535</v>
+        <v>5834.84</v>
       </c>
       <c r="G89">
         <v>861.8</v>
@@ -8591,37 +8591,37 @@
         <v>405.805</v>
       </c>
       <c r="M89">
-        <v>1360.220553</v>
+        <v>1375.855272</v>
       </c>
       <c r="N89">
-        <v>-954.415553</v>
+        <v>-970.0502719999999</v>
       </c>
       <c r="O89">
-        <v>-95.4415553</v>
+        <v>-97.0050272</v>
       </c>
       <c r="P89">
-        <v>-858.9739977</v>
+        <v>-873.0452448</v>
       </c>
       <c r="Q89">
-        <v>-853.4039977</v>
+        <v>-867.4752447999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2118483376001843</v>
+        <v>0.2256856990668663</v>
       </c>
       <c r="T89">
-        <v>3.328216418642813</v>
+        <v>3.605567786863048</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02983376476005947</v>
+        <v>0.02949474470596788</v>
       </c>
       <c r="W89">
-        <v>0.228765198269578</v>
+        <v>0.2288451391983328</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2983376476005947</v>
+        <v>0.2949474470596789</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2284660063825568</v>
+        <v>0.2303660063825568</v>
       </c>
       <c r="C90">
-        <v>-3612.338568683816</v>
+        <v>-3690.906096482116</v>
       </c>
       <c r="D90">
-        <v>1360.701431316184</v>
+        <v>1348.438903517884</v>
       </c>
       <c r="E90">
-        <v>3948.24</v>
+        <v>4014.545000000001</v>
       </c>
       <c r="F90">
-        <v>5834.84</v>
+        <v>5901.145</v>
       </c>
       <c r="G90">
         <v>861.8</v>
@@ -8673,37 +8673,37 @@
         <v>405.805</v>
       </c>
       <c r="M90">
-        <v>1375.855272</v>
+        <v>1391.489991</v>
       </c>
       <c r="N90">
-        <v>-970.0502719999999</v>
+        <v>-985.6849910000001</v>
       </c>
       <c r="O90">
-        <v>-97.0050272</v>
+        <v>-98.56849910000001</v>
       </c>
       <c r="P90">
-        <v>-873.0452448</v>
+        <v>-887.1164919</v>
       </c>
       <c r="Q90">
-        <v>-867.4752447999999</v>
+        <v>-881.5464919</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2256856990668663</v>
+        <v>0.2420389444365814</v>
       </c>
       <c r="T90">
-        <v>3.605567786863048</v>
+        <v>3.93334667657787</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02949474470596788</v>
+        <v>0.02916334308005813</v>
       </c>
       <c r="W90">
-        <v>0.2288451391983328</v>
+        <v>0.2289232837017223</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2949474470596789</v>
+        <v>0.2916334308005814</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2303660063825568</v>
+        <v>0.2322660063825568</v>
       </c>
       <c r="C91">
-        <v>-3690.906096482116</v>
+        <v>-3769.254580529113</v>
       </c>
       <c r="D91">
-        <v>1348.438903517884</v>
+        <v>1336.395419470887</v>
       </c>
       <c r="E91">
-        <v>4014.545000000001</v>
+        <v>4080.85</v>
       </c>
       <c r="F91">
-        <v>5901.145</v>
+        <v>5967.45</v>
       </c>
       <c r="G91">
         <v>861.8</v>
@@ -8755,37 +8755,37 @@
         <v>405.805</v>
       </c>
       <c r="M91">
-        <v>1391.489991</v>
+        <v>1407.12471</v>
       </c>
       <c r="N91">
-        <v>-985.6849910000001</v>
+        <v>-1001.31971</v>
       </c>
       <c r="O91">
-        <v>-98.56849910000001</v>
+        <v>-100.131971</v>
       </c>
       <c r="P91">
-        <v>-887.1164919</v>
+        <v>-901.187739</v>
       </c>
       <c r="Q91">
-        <v>-881.5464919</v>
+        <v>-895.6177389999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2420389444365814</v>
+        <v>0.2616628388802396</v>
       </c>
       <c r="T91">
-        <v>3.93334667657787</v>
+        <v>4.326681344235658</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02916334308005813</v>
+        <v>0.02883930593472415</v>
       </c>
       <c r="W91">
-        <v>0.2289232837017223</v>
+        <v>0.2289996916605921</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2916334308005814</v>
+        <v>0.2883930593472416</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2322660063825568</v>
+        <v>0.2341660063825568</v>
       </c>
       <c r="C92">
-        <v>-3769.254580529113</v>
+        <v>-3847.389837989253</v>
       </c>
       <c r="D92">
-        <v>1336.395419470887</v>
+        <v>1324.565162010748</v>
       </c>
       <c r="E92">
-        <v>4080.85</v>
+        <v>4147.155000000001</v>
       </c>
       <c r="F92">
-        <v>5967.45</v>
+        <v>6033.755</v>
       </c>
       <c r="G92">
         <v>861.8</v>
@@ -8837,37 +8837,37 @@
         <v>405.805</v>
       </c>
       <c r="M92">
-        <v>1407.12471</v>
+        <v>1422.759429</v>
       </c>
       <c r="N92">
-        <v>-1001.31971</v>
+        <v>-1016.954429</v>
       </c>
       <c r="O92">
-        <v>-100.131971</v>
+        <v>-101.6954429</v>
       </c>
       <c r="P92">
-        <v>-901.187739</v>
+        <v>-915.2589861000001</v>
       </c>
       <c r="Q92">
-        <v>-895.6177389999999</v>
+        <v>-909.6889861000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2616628388802396</v>
+        <v>0.2856475987558218</v>
       </c>
       <c r="T92">
-        <v>4.326681344235658</v>
+        <v>4.807423715817398</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02883930593472415</v>
+        <v>0.02852239048489201</v>
       </c>
       <c r="W92">
-        <v>0.2289996916605921</v>
+        <v>0.2290744203236625</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2883930593472416</v>
+        <v>0.2852239048489201</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2341660063825568</v>
+        <v>0.2360660063825568</v>
       </c>
       <c r="C93">
-        <v>-3847.389837989253</v>
+        <v>-3925.317481851805</v>
       </c>
       <c r="D93">
-        <v>1324.565162010748</v>
+        <v>1312.942518148195</v>
       </c>
       <c r="E93">
-        <v>4147.155000000001</v>
+        <v>4213.460000000001</v>
       </c>
       <c r="F93">
-        <v>6033.755</v>
+        <v>6100.06</v>
       </c>
       <c r="G93">
         <v>861.8</v>
@@ -8919,37 +8919,37 @@
         <v>405.805</v>
       </c>
       <c r="M93">
-        <v>1422.759429</v>
+        <v>1438.394148</v>
       </c>
       <c r="N93">
-        <v>-1016.954429</v>
+        <v>-1032.589148</v>
       </c>
       <c r="O93">
-        <v>-101.6954429</v>
+        <v>-103.2589148</v>
       </c>
       <c r="P93">
-        <v>-915.2589861000001</v>
+        <v>-929.3302332000001</v>
       </c>
       <c r="Q93">
-        <v>-909.6889861000001</v>
+        <v>-923.7602332</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2856475987558218</v>
+        <v>0.3156285486002996</v>
       </c>
       <c r="T93">
-        <v>4.807423715817398</v>
+        <v>5.408351680294574</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02852239048489201</v>
+        <v>0.02821236450136058</v>
       </c>
       <c r="W93">
-        <v>0.2290744203236625</v>
+        <v>0.2291475244505792</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2852239048489201</v>
+        <v>0.2821236450136059</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2360660063825568</v>
+        <v>0.2379660063825568</v>
       </c>
       <c r="C94">
-        <v>-3925.317481851805</v>
+        <v>-4003.042929810816</v>
       </c>
       <c r="D94">
-        <v>1312.942518148195</v>
+        <v>1301.522070189185</v>
       </c>
       <c r="E94">
-        <v>4213.460000000001</v>
+        <v>4279.765000000001</v>
       </c>
       <c r="F94">
-        <v>6100.06</v>
+        <v>6166.365000000001</v>
       </c>
       <c r="G94">
         <v>861.8</v>
@@ -9001,37 +9001,37 @@
         <v>405.805</v>
       </c>
       <c r="M94">
-        <v>1438.394148</v>
+        <v>1454.028867</v>
       </c>
       <c r="N94">
-        <v>-1032.589148</v>
+        <v>-1048.223867</v>
       </c>
       <c r="O94">
-        <v>-103.2589148</v>
+        <v>-104.8223867</v>
       </c>
       <c r="P94">
-        <v>-929.3302332000001</v>
+        <v>-943.4014803000001</v>
       </c>
       <c r="Q94">
-        <v>-923.7602332</v>
+        <v>-937.8314803000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3156285486002996</v>
+        <v>0.3541754841146281</v>
       </c>
       <c r="T94">
-        <v>5.408351680294574</v>
+        <v>6.180973348908084</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02821236450136058</v>
+        <v>0.02790900574328144</v>
       </c>
       <c r="W94">
-        <v>0.2291475244505792</v>
+        <v>0.2292190564457342</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2821236450136059</v>
+        <v>0.2790900574328143</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2379660063825568</v>
+        <v>0.2398660063825568</v>
       </c>
       <c r="C95">
-        <v>-4003.042929810816</v>
+        <v>-4080.571412685596</v>
       </c>
       <c r="D95">
-        <v>1301.522070189185</v>
+        <v>1290.298587314404</v>
       </c>
       <c r="E95">
-        <v>4279.765000000001</v>
+        <v>4346.07</v>
       </c>
       <c r="F95">
-        <v>6166.365000000001</v>
+        <v>6232.67</v>
       </c>
       <c r="G95">
         <v>861.8</v>
@@ -9083,37 +9083,37 @@
         <v>405.805</v>
       </c>
       <c r="M95">
-        <v>1454.028867</v>
+        <v>1469.663586</v>
       </c>
       <c r="N95">
-        <v>-1048.223867</v>
+        <v>-1063.858586</v>
       </c>
       <c r="O95">
-        <v>-104.8223867</v>
+        <v>-106.3858586</v>
       </c>
       <c r="P95">
-        <v>-943.4014803000001</v>
+        <v>-957.4727274000001</v>
       </c>
       <c r="Q95">
-        <v>-937.8314803000001</v>
+        <v>-951.9027274</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3541754841146281</v>
+        <v>0.4055713981337329</v>
       </c>
       <c r="T95">
-        <v>6.180973348908084</v>
+        <v>7.211135573726102</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02790900574328144</v>
+        <v>0.02761210142686354</v>
       </c>
       <c r="W95">
-        <v>0.2292190564457342</v>
+        <v>0.2292890664835456</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2790900574328143</v>
+        <v>0.2761210142686356</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2398660063825568</v>
+        <v>0.2417660063825568</v>
       </c>
       <c r="C96">
-        <v>-4080.571412685596</v>
+        <v>-4157.907982409277</v>
       </c>
       <c r="D96">
-        <v>1290.298587314404</v>
+        <v>1279.267017590723</v>
       </c>
       <c r="E96">
-        <v>4346.07</v>
+        <v>4412.375</v>
       </c>
       <c r="F96">
-        <v>6232.67</v>
+        <v>6298.975</v>
       </c>
       <c r="G96">
         <v>861.8</v>
@@ -9165,37 +9165,37 @@
         <v>405.805</v>
       </c>
       <c r="M96">
-        <v>1469.663586</v>
+        <v>1485.298305</v>
       </c>
       <c r="N96">
-        <v>-1063.858586</v>
+        <v>-1079.493305</v>
       </c>
       <c r="O96">
-        <v>-106.3858586</v>
+        <v>-107.9493305</v>
       </c>
       <c r="P96">
-        <v>-957.4727274000001</v>
+        <v>-971.5439745000001</v>
       </c>
       <c r="Q96">
-        <v>-951.9027274</v>
+        <v>-965.9739745000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4055713981337329</v>
+        <v>0.4775256777604797</v>
       </c>
       <c r="T96">
-        <v>7.211135573726102</v>
+        <v>8.653362688471324</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02761210142686354</v>
+        <v>0.0273214477276334</v>
       </c>
       <c r="W96">
-        <v>0.2292890664835456</v>
+        <v>0.2293576026258241</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2761210142686356</v>
+        <v>0.2732144772763341</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2417660063825568</v>
+        <v>0.2436660063825568</v>
       </c>
       <c r="C97">
-        <v>-4157.907982409277</v>
+        <v>-4235.057519611027</v>
       </c>
       <c r="D97">
-        <v>1279.267017590723</v>
+        <v>1268.422480388974</v>
       </c>
       <c r="E97">
-        <v>4412.375</v>
+        <v>4478.68</v>
       </c>
       <c r="F97">
-        <v>6298.975</v>
+        <v>6365.280000000001</v>
       </c>
       <c r="G97">
         <v>861.8</v>
@@ -9247,37 +9247,37 @@
         <v>405.805</v>
       </c>
       <c r="M97">
-        <v>1485.298305</v>
+        <v>1500.933024</v>
       </c>
       <c r="N97">
-        <v>-1079.493305</v>
+        <v>-1095.128024</v>
       </c>
       <c r="O97">
-        <v>-107.9493305</v>
+        <v>-109.5128024</v>
       </c>
       <c r="P97">
-        <v>-971.5439745000001</v>
+        <v>-985.6152216</v>
       </c>
       <c r="Q97">
-        <v>-965.9739745000001</v>
+        <v>-980.0452216</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4775256777604797</v>
+        <v>0.5854570972005998</v>
       </c>
       <c r="T97">
-        <v>8.653362688471324</v>
+        <v>10.81670336058916</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0273214477276334</v>
+        <v>0.02703684931380389</v>
       </c>
       <c r="W97">
-        <v>0.2293576026258241</v>
+        <v>0.2294247109318051</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2732144772763341</v>
+        <v>0.2703684931380389</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2436660063825568</v>
+        <v>0.2455660063825568</v>
       </c>
       <c r="C98">
-        <v>-4235.057519611026</v>
+        <v>-4312.024740815863</v>
       </c>
       <c r="D98">
-        <v>1268.422480388974</v>
+        <v>1257.760259184138</v>
       </c>
       <c r="E98">
-        <v>4478.68</v>
+        <v>4544.985000000001</v>
       </c>
       <c r="F98">
-        <v>6365.28</v>
+        <v>6431.585</v>
       </c>
       <c r="G98">
         <v>861.8</v>
@@ -9329,37 +9329,37 @@
         <v>405.805</v>
       </c>
       <c r="M98">
-        <v>1500.933024</v>
+        <v>1516.567743</v>
       </c>
       <c r="N98">
-        <v>-1095.128024</v>
+        <v>-1110.762743</v>
       </c>
       <c r="O98">
-        <v>-109.5128024</v>
+        <v>-111.0762743</v>
       </c>
       <c r="P98">
-        <v>-985.6152215999998</v>
+        <v>-999.6864687</v>
       </c>
       <c r="Q98">
-        <v>-980.0452215999998</v>
+        <v>-994.1164686999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5854570972005984</v>
+        <v>0.7653427962674646</v>
       </c>
       <c r="T98">
-        <v>10.81670336058913</v>
+        <v>14.42227114745218</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0270368493138039</v>
+        <v>0.02675811890850695</v>
       </c>
       <c r="W98">
-        <v>0.2294247109318051</v>
+        <v>0.2294904355613741</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.270368493138039</v>
+        <v>0.2675811890850694</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2455660063825568</v>
+        <v>0.2474660063825568</v>
       </c>
       <c r="C99">
-        <v>-4312.024740815863</v>
+        <v>-4388.814205284372</v>
       </c>
       <c r="D99">
-        <v>1257.760259184138</v>
+        <v>1247.275794715629</v>
       </c>
       <c r="E99">
-        <v>4544.985000000001</v>
+        <v>4611.290000000001</v>
       </c>
       <c r="F99">
-        <v>6431.585</v>
+        <v>6497.89</v>
       </c>
       <c r="G99">
         <v>861.8</v>
@@ -9411,37 +9411,37 @@
         <v>405.805</v>
       </c>
       <c r="M99">
-        <v>1516.567743</v>
+        <v>1532.202462</v>
       </c>
       <c r="N99">
-        <v>-1110.762743</v>
+        <v>-1126.397462</v>
       </c>
       <c r="O99">
-        <v>-111.0762743</v>
+        <v>-112.6397462</v>
       </c>
       <c r="P99">
-        <v>-999.6864687</v>
+        <v>-1013.7577158</v>
       </c>
       <c r="Q99">
-        <v>-994.1164686999999</v>
+        <v>-1008.1877158</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7653427962674646</v>
+        <v>1.125114194401197</v>
       </c>
       <c r="T99">
-        <v>14.42227114745218</v>
+        <v>21.63340672117826</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02675811890850695</v>
+        <v>0.0264850768788283</v>
       </c>
       <c r="W99">
-        <v>0.2294904355613741</v>
+        <v>0.2295548188719723</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2675811890850694</v>
+        <v>0.2648507687882831</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2474660063825568</v>
+        <v>0.2493660063825568</v>
       </c>
       <c r="C100">
-        <v>-4388.814205284372</v>
+        <v>-4465.430321513158</v>
       </c>
       <c r="D100">
-        <v>1247.275794715629</v>
+        <v>1236.964678486842</v>
       </c>
       <c r="E100">
-        <v>4611.290000000001</v>
+        <v>4677.594999999999</v>
       </c>
       <c r="F100">
-        <v>6497.89</v>
+        <v>6564.195</v>
       </c>
       <c r="G100">
         <v>861.8</v>
@@ -9493,37 +9493,37 @@
         <v>405.805</v>
       </c>
       <c r="M100">
-        <v>1532.202462</v>
+        <v>1547.837181</v>
       </c>
       <c r="N100">
-        <v>-1126.397462</v>
+        <v>-1142.032181</v>
       </c>
       <c r="O100">
-        <v>-112.6397462</v>
+        <v>-114.2032181</v>
       </c>
       <c r="P100">
-        <v>-1013.7577158</v>
+        <v>-1027.8289629</v>
       </c>
       <c r="Q100">
-        <v>-1008.1877158</v>
+        <v>-1022.2589629</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.125114194401197</v>
+        <v>2.204428388802393</v>
       </c>
       <c r="T100">
-        <v>21.63340672117826</v>
+        <v>43.26681344235653</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0264850768788283</v>
+        <v>0.02621755084974923</v>
       </c>
       <c r="W100">
-        <v>0.2295548188719723</v>
+        <v>0.2296179015096292</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2648507687882831</v>
+        <v>0.2621755084974923</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2493660063825568</v>
-      </c>
-      <c r="C101">
-        <v>-4465.430321513158</v>
-      </c>
-      <c r="D101">
-        <v>1236.964678486842</v>
-      </c>
-      <c r="E101">
-        <v>4677.594999999999</v>
-      </c>
-      <c r="F101">
-        <v>6564.195</v>
-      </c>
-      <c r="G101">
-        <v>861.8</v>
-      </c>
-      <c r="H101">
-        <v>4743.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>411.375</v>
-      </c>
-      <c r="K101">
-        <v>5.57</v>
-      </c>
-      <c r="L101">
-        <v>405.805</v>
-      </c>
-      <c r="M101">
-        <v>1547.837181</v>
-      </c>
-      <c r="N101">
-        <v>-1142.032181</v>
-      </c>
-      <c r="O101">
-        <v>-114.2032181</v>
-      </c>
-      <c r="P101">
-        <v>-1027.8289629</v>
-      </c>
-      <c r="Q101">
-        <v>-1022.2589629</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.204428388802393</v>
-      </c>
-      <c r="T101">
-        <v>43.26681344235653</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02621755084974923</v>
-      </c>
-      <c r="W101">
-        <v>0.2296179015096292</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2621755084974923</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
